--- a/Breakdown/Excel/Arm Info.xlsx
+++ b/Breakdown/Excel/Arm Info.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Udin\Kuliah\7. TUGAS AKHIR\Arm Manipulator\Breakdown\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09461132-31A2-4B67-BF21-449D37951A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9080F07-A07B-4879-BD58-9D4C266A8DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{313879A8-645A-4312-965B-79C9BD650931}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{313879A8-645A-4312-965B-79C9BD650931}"/>
   </bookViews>
   <sheets>
     <sheet name="Stepper Information" sheetId="1" r:id="rId1"/>
-    <sheet name="DH Param" sheetId="2" r:id="rId2"/>
+    <sheet name="Kinematics Overview" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
-  <si>
-    <t>DH</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="129">
   <si>
     <t>No</t>
   </si>
@@ -41,9 +38,6 @@
   </si>
   <si>
     <t>J1</t>
-  </si>
-  <si>
-    <t>Ratio</t>
   </si>
   <si>
     <t>J2</t>
@@ -72,10 +66,6 @@
   <si>
     <t>Total Step
 Per Rev</t>
-  </si>
-  <si>
-    <t>Driver
-Step</t>
   </si>
   <si>
     <r>
@@ -163,27 +153,346 @@
 Rev/sec</t>
   </si>
   <si>
+    <t>Θ</t>
+  </si>
+  <si>
+    <t>α</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>DH PARAMETER</t>
+  </si>
+  <si>
+    <t>Radians</t>
+  </si>
+  <si>
+    <t>INPUTS</t>
+  </si>
+  <si>
+    <t>JOINTS</t>
+  </si>
+  <si>
+    <t>Degrees</t>
+  </si>
+  <si>
+    <t>OUTPUTS</t>
+  </si>
+  <si>
+    <t>FORWARD KINEMATICS</t>
+  </si>
+  <si>
+    <t>J1 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>J2 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>J3 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>J4 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>J5 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>J6 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>R0-2 MATRIX</t>
+  </si>
+  <si>
+    <t>R0-3 MATRIX</t>
+  </si>
+  <si>
+    <t>Param</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Xpos</t>
+  </si>
+  <si>
+    <t>Ypos</t>
+  </si>
+  <si>
+    <t>Zpos</t>
+  </si>
+  <si>
+    <t>Rx</t>
+  </si>
+  <si>
+    <t>Rz</t>
+  </si>
+  <si>
+    <t>Ry</t>
+  </si>
+  <si>
+    <t>TOOLFRAME TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>Angles</t>
+  </si>
+  <si>
+    <t>Toolframe</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>INVERSE KINEMATICS</t>
+  </si>
+  <si>
+    <t>PARAMETERS</t>
+  </si>
+  <si>
+    <t>R0-6 TRANSFORMATION MATRIX REVERSE</t>
+  </si>
+  <si>
+    <t>INVERT TOOLFRAME TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>R0-T TRANSFORMATION MATRIX REVERSE</t>
+  </si>
+  <si>
+    <t>R0-6 TRANSFORMATION MATRIX NEGATE</t>
+  </si>
+  <si>
+    <t>R0-5 TRANSFORMATION MATRIX REVERSE</t>
+  </si>
+  <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>3rd</t>
+  </si>
+  <si>
+    <t>4th</t>
+  </si>
+  <si>
+    <t>5th</t>
+  </si>
+  <si>
+    <t>6th</t>
+  </si>
+  <si>
+    <t>7th</t>
+  </si>
+  <si>
+    <t>8th</t>
+  </si>
+  <si>
+    <t>9th</t>
+  </si>
+  <si>
+    <t>10th</t>
+  </si>
+  <si>
+    <t>11th</t>
+  </si>
+  <si>
+    <t>12th</t>
+  </si>
+  <si>
+    <t>13th</t>
+  </si>
+  <si>
+    <t>J1 ∠</t>
+  </si>
+  <si>
+    <t>IK ANALYSIS</t>
+  </si>
+  <si>
+    <t>R0-5 @J1 ZERO</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>ΘB</t>
+  </si>
+  <si>
+    <t>ΘC</t>
+  </si>
+  <si>
+    <t>ΘD</t>
+  </si>
+  <si>
+    <t>CALCULATE J1 ANGLE</t>
+  </si>
+  <si>
+    <t>14th</t>
+  </si>
+  <si>
+    <t>R0-3 MATRIX TRANSPOSED</t>
+  </si>
+  <si>
+    <t>15th</t>
+  </si>
+  <si>
+    <t>R3-6 WIRST ORIENTATION</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>(-170 / 170)</t>
+  </si>
+  <si>
+    <t>(-155 / 155)</t>
+  </si>
+  <si>
+    <t>(-105 / 105)</t>
+  </si>
+  <si>
+    <t>(-165 / 165)</t>
+  </si>
+  <si>
+    <t>SINGULARITY AVOIDANCE</t>
+  </si>
+  <si>
+    <t>T0-2 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>T0-3 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>T0-4 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>T0-5 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>T0-6 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>T0-E TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>T0-1 TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>JOINTS Z-AXES</t>
+  </si>
+  <si>
+    <t>Joints</t>
+  </si>
+  <si>
+    <t>JACOBIANS VALUE</t>
+  </si>
+  <si>
+    <t>Linear Vel.</t>
+  </si>
+  <si>
+    <t>Angular Vel.</t>
+  </si>
+  <si>
+    <t>JACOBIAN MATRIX</t>
+  </si>
+  <si>
+    <t>JACOBIAN STATE</t>
+  </si>
+  <si>
+    <t>T0-1</t>
+  </si>
+  <si>
+    <t>T0-2</t>
+  </si>
+  <si>
+    <t>T0-3</t>
+  </si>
+  <si>
+    <t>T0-4</t>
+  </si>
+  <si>
+    <t>T0-5</t>
+  </si>
+  <si>
+    <t>PE-Pi</t>
+  </si>
+  <si>
+    <t>JOINTS ORIGIN POSITION</t>
+  </si>
+  <si>
+    <t>BASE TRANSFORMATION MATRIX</t>
+  </si>
+  <si>
+    <t>SETUP</t>
+  </si>
+  <si>
+    <t>T0-6</t>
+  </si>
+  <si>
+    <t>Driver
+Step
+Config</t>
+  </si>
+  <si>
+    <t>Min
+Rev/min
+Config</t>
+  </si>
+  <si>
+    <t>Max
+Rev/min
+Config</t>
+  </si>
+  <si>
+    <t>Gear
+Ratio</t>
+  </si>
+  <si>
     <t>Max 1 Rev
-Time</t>
+Time (s)</t>
   </si>
   <si>
     <t>Max 1/6 Rev
-Time</t>
-  </si>
-  <si>
-    <t>Rev/min
-Max</t>
-  </si>
-  <si>
-    <t>Rev/min
-Min</t>
+Time (s)</t>
+  </si>
+  <si>
+    <t>ANGLE AND POSITION LIMITATION</t>
+  </si>
+  <si>
+    <t>(-60 / 90)</t>
+  </si>
+  <si>
+    <t>(-90 / 60)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.E+00"/>
+    <numFmt numFmtId="166" formatCode="0.0.E+00"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,8 +517,63 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,8 +586,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -283,11 +659,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -304,6 +759,75 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -317,6 +841,84 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -334,6 +936,848 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>439819</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>115986</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>745880</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C822721-7ED2-79A1-189F-64750AD92768}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15336919" y="6269136"/>
+          <a:ext cx="2942581" cy="3560664"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>273129</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>10884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>703637</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E153EC5F-A660-4291-AB95-C90481319E67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15170229" y="639534"/>
+          <a:ext cx="3072743" cy="1436915"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>329292</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>52942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>723422</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>175259</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9842AFB9-BF22-430A-8409-D103A387BB8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13473792" y="4682092"/>
+          <a:ext cx="3899330" cy="1261507"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>653784</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>128549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>535641</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{801237CD-EDBE-4DA6-9139-CDDEE0929D49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect r="4612"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13798284" y="2852699"/>
+          <a:ext cx="3387057" cy="1433551"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>780439</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>129680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>250522</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23A42A1B-ADF8-4901-8B44-98F27581FEB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27428668" y="946109"/>
+          <a:ext cx="3890227" cy="1350777"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>343724</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>472710</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>15784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB93A2AC-DC28-4E32-B592-ECBD0EDDA34B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25228467" y="673704"/>
+          <a:ext cx="1881042" cy="1631346"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>607359</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>55318</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>434884</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>60959</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B407EAB4-9089-453D-BD8D-31B35B325C74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31835504" y="7356663"/>
+          <a:ext cx="4969986" cy="2343250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>531037</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>172176</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>515051</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B97F3A56-76AD-4752-86BA-97A07EC1A15C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="34706737" y="2896326"/>
+          <a:ext cx="1803289" cy="837474"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>178213</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>124691</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>245710</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5327112-DC07-2572-ACA8-5C3B4297125D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12446413" y="6277841"/>
+          <a:ext cx="2700207" cy="3532909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>584404</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>183126</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>332508</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="19" name="Group 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06599109-9C07-ACD4-0811-B15B8C6A412C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="31641347" y="770955"/>
+          <a:ext cx="3068247" cy="3063538"/>
+          <a:chOff x="31835369" y="765832"/>
+          <a:chExt cx="3074010" cy="2975812"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="11" name="Picture 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E16DB6E-25D2-266F-4120-4613A305C0B7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="31835369" y="765832"/>
+            <a:ext cx="3074010" cy="2975812"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="16" name="TextBox 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECD23277-3FD3-8B8A-5064-6D7D2A6C586C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="34164494" y="1201271"/>
+            <a:ext cx="740074" cy="436786"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1100"/>
+              <a:t>WIRST</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1100" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1100" baseline="0"/>
+              <a:t>POSITION</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-ID" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>612757</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>32993</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>22897</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>87074</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="18" name="Group 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4E31B88-3E71-AE83-DAAF-8EF9AC596D94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="31669700" y="4180450"/>
+          <a:ext cx="4559083" cy="3014995"/>
+          <a:chOff x="31863722" y="4076075"/>
+          <a:chExt cx="4564846" cy="2922787"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="13" name="Picture 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C2B2E09-8E62-9F21-FDED-CA57DDAD828B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="31863722" y="4076075"/>
+            <a:ext cx="4528094" cy="2922787"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="TextBox 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C2C6413-3FFA-4C92-ADEB-501DF0D74DD6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="35688494" y="5100918"/>
+            <a:ext cx="740074" cy="436786"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1100"/>
+              <a:t>WIRST</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1100" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1100" baseline="0"/>
+              <a:t>POSITION</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-ID" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>833104</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>213208</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>21972</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{305448F5-18E2-4975-83AF-D04FFAAE6EB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15822733" y="13628914"/>
+          <a:ext cx="2029142" cy="1314107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>21770</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>32655</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>511275</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>55788</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF628CB9-169C-8640-8B93-16C3F7B9D84E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8839199" y="13650684"/>
+          <a:ext cx="6650275" cy="1328058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>489856</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>119743</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>594009</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>97427</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD5D9BA9-BB77-50B4-71A4-E3657E7B0E77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14597742" y="11332029"/>
+          <a:ext cx="2753191" cy="1654628"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -638,107 +2082,107 @@
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" style="2" customWidth="1"/>
     <col min="4" max="7" width="8.88671875" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" style="2"/>
-    <col min="9" max="9" width="2.77734375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="2.77734375" style="30" customWidth="1"/>
     <col min="10" max="10" width="4.77734375" style="2" customWidth="1"/>
     <col min="11" max="13" width="8.88671875" style="2"/>
-    <col min="14" max="14" width="2.77734375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="2.77734375" style="30" customWidth="1"/>
     <col min="15" max="15" width="4.77734375" style="2" customWidth="1"/>
     <col min="18" max="20" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="J1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="O1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="10"/>
+      <c r="A1" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="J1" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="O1" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="33"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>5</v>
+        <v>122</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="I2" s="30"/>
       <c r="J2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="30"/>
+      <c r="O2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="7"/>
-      <c r="O2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="U2" s="5" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -746,10 +2190,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3">
         <v>800</v>
@@ -771,43 +2215,43 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="3">
+        <f t="shared" ref="L3:L8" si="0">E3*D3/60</f>
+        <v>2400</v>
+      </c>
+      <c r="M3" s="3">
+        <f t="shared" ref="M3:M8" si="1">F3*D3/60</f>
+        <v>4800</v>
+      </c>
+      <c r="O3" s="3">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="15">
+        <f t="shared" ref="Q3:Q8" si="2">E3/G3</f>
+        <v>2</v>
+      </c>
+      <c r="R3" s="15">
+        <f t="shared" ref="R3:R8" si="3">F3/G3</f>
         <v>4</v>
       </c>
-      <c r="L3" s="3">
-        <f>E3*D3/60</f>
-        <v>2400</v>
-      </c>
-      <c r="M3" s="3">
-        <f>F3*D3/60</f>
-        <v>4800</v>
-      </c>
-      <c r="O3" s="3">
-        <v>1</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="3">
-        <f>E3/G3</f>
-        <v>2</v>
-      </c>
-      <c r="R3" s="3">
-        <f>F3/G3</f>
-        <v>4</v>
-      </c>
-      <c r="S3" s="3">
+      <c r="S3" s="15">
         <f>Q3/60</f>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="15">
         <f>R3/60</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="15">
         <f>1/T3</f>
         <v>15</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="15">
         <f>U3/6</f>
         <v>2.5</v>
       </c>
@@ -817,10 +2261,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>800</v>
@@ -842,44 +2286,44 @@
         <v>2</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3">
-        <f t="shared" ref="L4:L8" si="0">E4*D4/60</f>
+        <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="M4" s="3">
-        <f>F4*D4/60</f>
+        <f t="shared" si="1"/>
         <v>4200</v>
       </c>
       <c r="O4" s="3">
         <v>2</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q4" s="3">
-        <f t="shared" ref="Q4:Q8" si="1">E4/G4</f>
+        <v>4</v>
+      </c>
+      <c r="Q4" s="15">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="R4" s="3">
-        <f>F4/G4</f>
+      <c r="R4" s="15">
+        <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
-      <c r="S4" s="3">
-        <f t="shared" ref="S4:S8" si="2">Q4/60</f>
+      <c r="S4" s="15">
+        <f t="shared" ref="S4:S8" si="4">Q4/60</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="T4" s="3">
-        <f t="shared" ref="T4:T8" si="3">R4/60</f>
+      <c r="T4" s="15">
+        <f t="shared" ref="T4:T8" si="5">R4/60</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="U4" s="3">
-        <f t="shared" ref="U4:U8" si="4">1/T4</f>
+      <c r="U4" s="15">
+        <f t="shared" ref="U4:U8" si="6">1/T4</f>
         <v>6.8571428571428568</v>
       </c>
-      <c r="V4" s="3">
-        <f t="shared" ref="V4:V8" si="5">U4/6</f>
+      <c r="V4" s="15">
+        <f t="shared" ref="V4:V8" si="7">U4/6</f>
         <v>1.1428571428571428</v>
       </c>
     </row>
@@ -888,10 +2332,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3">
         <v>800</v>
@@ -913,44 +2357,44 @@
         <v>3</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="M5" s="3">
-        <f>F5*D5/60</f>
+        <f t="shared" si="1"/>
         <v>4800</v>
       </c>
       <c r="O5" s="3">
         <v>3</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q5" s="3">
-        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="R5" s="3">
-        <f>F5/G5</f>
+      <c r="Q5" s="15">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="R5" s="15">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="S5" s="3">
-        <f t="shared" si="2"/>
+      <c r="S5" s="15">
+        <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="T5" s="3">
-        <f t="shared" si="3"/>
+      <c r="T5" s="15">
+        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="U5" s="3">
-        <f t="shared" si="4"/>
+      <c r="U5" s="15">
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="V5" s="3">
-        <f t="shared" si="5"/>
+      <c r="V5" s="15">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -959,10 +2403,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3">
         <v>800</v>
@@ -984,44 +2428,44 @@
         <v>4</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="M6" s="3">
-        <f>F6*D6/60</f>
+        <f t="shared" si="1"/>
         <v>4800</v>
       </c>
       <c r="O6" s="3">
         <v>4</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="3">
-        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="R6" s="3">
-        <f>F6/G6</f>
+      <c r="R6" s="15">
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="S6" s="3">
-        <f t="shared" si="2"/>
+      <c r="S6" s="15">
+        <f t="shared" si="4"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="T6" s="3">
-        <f t="shared" si="3"/>
+      <c r="T6" s="15">
+        <f t="shared" si="5"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="U6" s="3">
-        <f t="shared" si="4"/>
+      <c r="U6" s="15">
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="V6" s="3">
-        <f t="shared" si="5"/>
+      <c r="V6" s="15">
+        <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
     </row>
@@ -1030,10 +2474,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3">
         <v>800</v>
@@ -1048,51 +2492,51 @@
         <v>90</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" ref="H7" si="6">G7*D7</f>
+        <f>G7*D7</f>
         <v>72000</v>
       </c>
       <c r="J7" s="3">
         <v>5</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="M7" s="3">
-        <f>F7*D7/60</f>
+        <f t="shared" si="1"/>
         <v>4800</v>
       </c>
       <c r="O7" s="3">
         <v>5</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="3">
-        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Q7" s="15">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="R7" s="3">
-        <f>F7/G7</f>
+      <c r="R7" s="15">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="S7" s="3">
-        <f t="shared" si="2"/>
+      <c r="S7" s="15">
+        <f t="shared" si="4"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="T7" s="3">
-        <f t="shared" si="3"/>
+      <c r="T7" s="15">
+        <f t="shared" si="5"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="U7" s="3">
-        <f t="shared" si="4"/>
+      <c r="U7" s="15">
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="V7" s="3">
-        <f t="shared" si="5"/>
+      <c r="V7" s="15">
+        <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
     </row>
@@ -1101,10 +2545,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3">
         <v>800</v>
@@ -1119,51 +2563,51 @@
         <v>9</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" ref="H8" si="7">G8*D7</f>
+        <f>G8*D7</f>
         <v>7200</v>
       </c>
       <c r="J8" s="3">
         <v>6</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="M8" s="3">
-        <f>F8*D8/60</f>
+        <f t="shared" si="1"/>
         <v>4800</v>
       </c>
       <c r="O8" s="3">
         <v>6</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="3">
-        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Q8" s="15">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="R8" s="3">
-        <f>F8/G8</f>
+      <c r="R8" s="15">
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="S8" s="3">
-        <f t="shared" si="2"/>
+      <c r="S8" s="15">
+        <f t="shared" si="4"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="T8" s="3">
-        <f t="shared" si="3"/>
+      <c r="T8" s="15">
+        <f t="shared" si="5"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="U8" s="3">
-        <f t="shared" si="4"/>
+      <c r="U8" s="15">
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="V8" s="3">
-        <f t="shared" si="5"/>
+      <c r="V8" s="15">
+        <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
     </row>
@@ -1181,15 +2625,3710 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF990D27-4B97-4251-AD4B-2BBC3FAFA5B8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AT83"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="21" width="12.88671875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="2.77734375" style="23" customWidth="1"/>
+    <col min="23" max="37" width="12.88671875" style="2" customWidth="1"/>
+    <col min="38" max="45" width="8.88671875" style="2" customWidth="1"/>
+    <col min="46" max="46" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="47" max="16384" width="8.88671875" style="2" hidden="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="1:45" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
+      <c r="AD1" s="42"/>
+      <c r="AE1" s="42"/>
+      <c r="AF1" s="42"/>
+      <c r="AG1" s="42"/>
+      <c r="AH1" s="42"/>
+      <c r="AI1" s="42"/>
+      <c r="AJ1" s="42"/>
+      <c r="AK1" s="42"/>
+      <c r="AL1" s="42"/>
+      <c r="AM1" s="42"/>
+      <c r="AN1" s="42"/>
+      <c r="AO1" s="42"/>
+      <c r="AP1" s="42"/>
+      <c r="AQ1" s="42"/>
+      <c r="AR1" s="42"/>
+      <c r="AS1" s="42"/>
+    </row>
+    <row r="2" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+    </row>
+    <row r="3" spans="1:45" ht="18" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="I3" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="O3" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="AA3" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+    </row>
+    <row r="4" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="56"/>
+      <c r="G4" s="57"/>
+      <c r="I4" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="24"/>
+      <c r="W4" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="X4" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB4" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC4" s="57"/>
+    </row>
+    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A5" s="54"/>
+      <c r="B5" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="47"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <f>RADIANS(C6)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <f>RADIANS(-90)</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="L6" s="6">
+        <v>191</v>
+      </c>
+      <c r="M6" s="6">
+        <v>23.5</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="6">
+        <f>N48</f>
+        <v>663.5</v>
+      </c>
+      <c r="Q6" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="V6" s="24"/>
+      <c r="W6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" s="6">
+        <f t="shared" ref="X6:X11" si="0">P6</f>
+        <v>663.5</v>
+      </c>
+      <c r="Y6" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="6">
+        <f>DEGREES(AC6)</f>
+        <v>-5.8643137630106747E-17</v>
+      </c>
+      <c r="AC6" s="6">
+        <f>Y32</f>
+        <v>-1.0235158353455473E-18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <f>RADIANS(C7)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="51"/>
+      <c r="I7" s="9">
+        <v>2</v>
+      </c>
+      <c r="J7" s="6">
+        <f>D7-RADIANS(90)</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="K7" s="6">
+        <f>RADIANS(0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>650</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" s="6">
+        <f>N49</f>
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="Q7" s="51"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="X7" s="6">
+        <f t="shared" si="0"/>
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="Y7" s="51"/>
+      <c r="AA7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB7" s="6">
+        <f>90-(AD36+AD37)</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="6">
+        <f>RADIANS(AB7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <f>RADIANS(C8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="52"/>
+      <c r="I8" s="9">
+        <v>3</v>
+      </c>
+      <c r="J8" s="6">
+        <f>D8+RADIANS(180)</f>
+        <v>3.1415926535897931</v>
+      </c>
+      <c r="K8" s="6">
+        <f>RADIANS(90)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="6">
+        <f>N50</f>
+        <v>841</v>
+      </c>
+      <c r="Q8" s="52"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="X8" s="6">
+        <f t="shared" si="0"/>
+        <v>841</v>
+      </c>
+      <c r="Y8" s="52"/>
+      <c r="AA8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB8" s="6">
+        <f>-(AD38)+90</f>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="6">
+        <f>RADIANS(AB8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <f t="shared" ref="D9:D11" si="1">RADIANS(C9)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <f>RADIANS(F9)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>4</v>
+      </c>
+      <c r="J9" s="6">
+        <f>D9</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <f>RADIANS(-90)</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="L9" s="6">
+        <v>575</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" s="6">
+        <f>DEGREES(Q9)</f>
+        <v>45</v>
+      </c>
+      <c r="Q9" s="6">
+        <f>ATAN2(K48/COS(Q10),K49/COS(Q10))</f>
+        <v>0.78539816339744828</v>
+      </c>
+      <c r="V9" s="24"/>
+      <c r="W9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="X9" s="6">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="Y9" s="6">
+        <f>RADIANS(X9)</f>
+        <v>0.78539816339744828</v>
+      </c>
+      <c r="AA9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="6">
+        <f>DEGREES(AC9)</f>
+        <v>106.58722401468049</v>
+      </c>
+      <c r="AC9" s="6">
+        <f>IF(AC10&gt;0, ATAN2(AI51,AI52),  ATAN2(-AI51,-AI52))</f>
+        <v>1.8602979996169433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <f>RADIANS(C10)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <f>RADIANS(F10)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>5</v>
+      </c>
+      <c r="J10" s="6">
+        <f>D10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <f>RADIANS(90)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="P10" s="6">
+        <f>DEGREES(Q10)</f>
+        <v>90</v>
+      </c>
+      <c r="Q10" s="6">
+        <f>ATAN2(SQRT(L50^2 + M50^2), -K50)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="V10" s="24"/>
+      <c r="W10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="X10" s="6">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="Y10" s="6">
+        <f t="shared" ref="Y10:Y11" si="2">RADIANS(X10)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AA10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="6">
+        <f>DEGREES(AC10)</f>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="6">
+        <f>IF(C10&gt;0,ATAN2(AI53,SQRT(1-AI53^2)), ATAN2(AI53,-SQRT(1-AI53^2)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <f>RADIANS(F11)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>6</v>
+      </c>
+      <c r="J11" s="6">
+        <f>D11</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <f>RADIANS(0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>65</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" s="6">
+        <f>DEGREES(Q11)</f>
+        <v>45</v>
+      </c>
+      <c r="Q11" s="6">
+        <f>ATAN2(M50/COS(Q10),L50/COS(Q10))</f>
+        <v>0.78539816339744828</v>
+      </c>
+      <c r="V11" s="24"/>
+      <c r="W11" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="X11" s="6">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="Y11" s="6">
+        <f t="shared" si="2"/>
+        <v>0.78539816339744828</v>
+      </c>
+      <c r="AA11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB11" s="6">
+        <f>DEGREES(AC11)</f>
+        <v>-106.58722401468049</v>
+      </c>
+      <c r="AC11" s="6">
+        <f>IF(AC10&gt;0, ATAN2(-AG53,AH53), ATAN2(AG53,-AH53))</f>
+        <v>-1.8602979996169433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="V12" s="24"/>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="V13" s="24"/>
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="B14" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="G14" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="36"/>
+      <c r="L14" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="36"/>
+      <c r="V14" s="24"/>
+      <c r="X14" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y14" s="36"/>
+      <c r="AC14" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD14" s="36"/>
+      <c r="AH14" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI14" s="36"/>
+    </row>
+    <row r="15" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A15" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="F15" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="K15" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AB15" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="35"/>
+      <c r="AG15" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="35"/>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <f>COS(J6)</f>
+        <v>1</v>
+      </c>
+      <c r="G16" s="6">
+        <f>-SIN(J6)*COS(K6)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <f>SIN(J6)*SIN(K6)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <f>M6*COS(J6)</f>
+        <v>23.5</v>
+      </c>
+      <c r="K16" s="6">
+        <f>COS(J7)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="L16" s="6">
+        <f>-SIN(J7)*COS(K7)</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="6">
+        <f>SIN(J7)*SIN(K7)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="6">
+        <f>M7*COS(J7)</f>
+        <v>3.981732478453015E-14</v>
+      </c>
+      <c r="V16" s="24"/>
+      <c r="W16" s="22">
+        <f>COS(RADIANS(X9))*COS(RADIANS(X10))</f>
+        <v>4.3315539021305322E-17</v>
+      </c>
+      <c r="X16" s="6">
+        <f>COS(RADIANS(X9))*SIN(RADIANS(X10))*SIN(RADIANS(X11))-SIN(RADIANS(X9))*COS(RADIANS(X11))</f>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="6">
+        <f>COS(RADIANS(X9))*SIN(RADIANS(X10))*COS(RADIANS(X11))+SIN(RADIANS(X9))*SIN(RADIANS(X11))</f>
+        <v>1</v>
+      </c>
+      <c r="Z16" s="6">
+        <f>X6</f>
+        <v>663.5</v>
+      </c>
+      <c r="AA16" s="18"/>
+      <c r="AB16" s="6">
+        <f t="shared" ref="AB16:AE19" si="3">F32</f>
+        <v>1</v>
+      </c>
+      <c r="AC16" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="18"/>
+      <c r="AG16" s="6">
+        <f>AB16</f>
+        <v>1</v>
+      </c>
+      <c r="AH16" s="6">
+        <f>AB17</f>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="6">
+        <f>AB18</f>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="6">
+        <f>((AE16*AG16)+(AE17*AH16)+(AE18*AI16))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>0</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <f>SIN(J6)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <f>COS(J6)*COS(K6)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="H17" s="6">
+        <f>-COS(J6)*SIN(K6)</f>
+        <v>1</v>
+      </c>
+      <c r="I17" s="6">
+        <f>M6*SIN(J6)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="6">
+        <f>SIN(J7)</f>
+        <v>-1</v>
+      </c>
+      <c r="L17" s="6">
+        <f>COS(J7)*COS(K7)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M17" s="6">
+        <f>-COS(J7)*SIN(K7)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <f>M7*SIN(J7)</f>
+        <v>-650</v>
+      </c>
+      <c r="V17" s="24"/>
+      <c r="W17" s="22">
+        <f>SIN(RADIANS(X9))*COS(RADIANS(X10))</f>
+        <v>4.3315539021305316E-17</v>
+      </c>
+      <c r="X17" s="6">
+        <f>SIN(RADIANS(X9))*SIN(RADIANS(X10))*SIN(RADIANS(X11))+COS(RADIANS(X9))*COS(RADIANS(X11))</f>
+        <v>1</v>
+      </c>
+      <c r="Y17" s="6">
+        <f>SIN(RADIANS(X9))*SIN(RADIANS(X10))*COS(RADIANS(X11))-COS(RADIANS(X9))*SIN(RADIANS(X11))</f>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="6">
+        <f>X7</f>
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="6">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AD17" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="18"/>
+      <c r="AG17" s="6">
+        <f>AC16</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="6">
+        <f>AC17</f>
+        <v>1</v>
+      </c>
+      <c r="AI17" s="6">
+        <f>AC18</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="6">
+        <f>((AE16*AG17)+(AE17*AH17)+(AE18*AI17))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>0</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <f>SIN(K6)</f>
+        <v>-1</v>
+      </c>
+      <c r="H18" s="6">
+        <f>COS(K6)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="I18" s="6">
+        <f>L6</f>
+        <v>191</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6">
+        <f>SIN(K7)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="6">
+        <f>COS(K7)</f>
+        <v>1</v>
+      </c>
+      <c r="N18" s="6">
+        <f>L7</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="24"/>
+      <c r="W18" s="22">
+        <f>-SIN(RADIANS(X10))</f>
+        <v>-1</v>
+      </c>
+      <c r="X18" s="6">
+        <f>COS(RADIANS(X10))*SIN(RADIANS(X11))</f>
+        <v>4.3315539021305316E-17</v>
+      </c>
+      <c r="Y18" s="6">
+        <f>COS(RADIANS(X10))*COS(RADIANS(X11))</f>
+        <v>4.3315539021305322E-17</v>
+      </c>
+      <c r="Z18" s="6">
+        <f>X8</f>
+        <v>841</v>
+      </c>
+      <c r="AA18" s="18"/>
+      <c r="AB18" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AE18" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="18"/>
+      <c r="AG18" s="6">
+        <f>AD16</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="6">
+        <f>AD17</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="6">
+        <f>AD18</f>
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="6">
+        <f>((AE16*AG18)+(AE17*AH18)+(AE18*AI18))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>0</v>
+      </c>
+      <c r="B19" s="6">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6">
+        <v>1</v>
+      </c>
+      <c r="V19" s="24"/>
+      <c r="W19" s="22">
+        <v>0</v>
+      </c>
+      <c r="X19" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="18"/>
+      <c r="AB19" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="6">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AF19" s="18"/>
+      <c r="AG19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="6">
+        <f>AE19</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V20" s="24"/>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V21" s="24"/>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B22" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="36"/>
+      <c r="G22" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="36"/>
+      <c r="L22" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22" s="36"/>
+      <c r="V22" s="24"/>
+      <c r="X22" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y22" s="36"/>
+      <c r="AC22" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD22" s="36"/>
+      <c r="AH22" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI22" s="36"/>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A23" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="F23" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="K23" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AB23" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC23" s="35"/>
+      <c r="AD23" s="35"/>
+      <c r="AE23" s="35"/>
+      <c r="AG23" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH23" s="35"/>
+      <c r="AI23" s="35"/>
+      <c r="AJ23" s="35"/>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <f>COS(J8)</f>
+        <v>-1</v>
+      </c>
+      <c r="B24" s="6">
+        <f>-SIN(J8)*COS(K8)</f>
+        <v>-7.5049436828248946E-33</v>
+      </c>
+      <c r="C24" s="6">
+        <f>SIN(J8)*SIN(K8)</f>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="D24" s="6">
+        <f>M8*COS(J8)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <f>COS(J9)</f>
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
+        <f>-SIN(J9)*COS(K9)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <f>SIN(J9)*SIN(K9)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="6">
+        <f>M9*COS(J9)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="6">
+        <f>COS(J10)</f>
+        <v>1</v>
+      </c>
+      <c r="L24" s="6">
+        <f>-SIN(J10)*COS(K10)</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
+        <f>SIN(J10)*SIN(K10)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="6">
+        <f>M10*COS(J10)</f>
+        <v>0</v>
+      </c>
+      <c r="V24" s="24"/>
+      <c r="W24" s="22">
+        <f t="array" ref="W24:Z27">MMULT(W16:Z19,AG16:AJ19)</f>
+        <v>4.3315539021305322E-17</v>
+      </c>
+      <c r="X24" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>663.5</v>
+      </c>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="6">
+        <f t="array" ref="AG24:AJ27">MMULT(W24:Z27,AB24:AE27)</f>
+        <v>4.3315539021305322E-17</v>
+      </c>
+      <c r="AH24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="6">
+        <v>598.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <f>SIN(J8)</f>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="B25" s="6">
+        <f>COS(J8)*COS(K8)</f>
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="C25" s="6">
+        <f>-COS(J8)*SIN(K8)</f>
+        <v>1</v>
+      </c>
+      <c r="D25" s="6">
+        <f>M8*SIN(J8)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <f>SIN(J9)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <f>COS(J9)*COS(K9)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="H25" s="6">
+        <f>-COS(J9)*SIN(K9)</f>
+        <v>1</v>
+      </c>
+      <c r="I25" s="6">
+        <f>M9*SIN(J9)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="6">
+        <f>SIN(J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="6">
+        <f>COS(J10)*COS(K10)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M25" s="6">
+        <f>-COS(J10)*SIN(K10)</f>
+        <v>-1</v>
+      </c>
+      <c r="N25" s="6">
+        <f>M10*SIN(J10)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="24"/>
+      <c r="W25" s="22">
+        <v>4.3315539021305316E-17</v>
+      </c>
+      <c r="X25" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="6">
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="AA25" s="18"/>
+      <c r="AB25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="18"/>
+      <c r="AG25" s="6">
+        <v>4.3315539021305316E-17</v>
+      </c>
+      <c r="AH25" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="6">
+        <v>-6.1257422745431001E-16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>0</v>
+      </c>
+      <c r="B26" s="6">
+        <f>SIN(K8)</f>
+        <v>1</v>
+      </c>
+      <c r="C26" s="6">
+        <f>COS(K8)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="D26" s="6">
+        <f>L8</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <f>SIN(K9)</f>
+        <v>-1</v>
+      </c>
+      <c r="H26" s="6">
+        <f>COS(K9)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="I26" s="6">
+        <f>L9</f>
+        <v>575</v>
+      </c>
+      <c r="K26" s="6">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6">
+        <f>SIN(K10)</f>
+        <v>1</v>
+      </c>
+      <c r="M26" s="6">
+        <f>COS(K10)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="N26" s="6">
+        <f>L10</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="24"/>
+      <c r="W26" s="22">
+        <v>-1</v>
+      </c>
+      <c r="X26" s="6">
+        <v>4.3315539021305316E-17</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>4.3315539021305322E-17</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>841</v>
+      </c>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="6">
+        <f>-L11</f>
+        <v>-65</v>
+      </c>
+      <c r="AF26" s="18"/>
+      <c r="AG26" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>4.3315539021305316E-17</v>
+      </c>
+      <c r="AI26" s="6">
+        <v>4.3315539021305322E-17</v>
+      </c>
+      <c r="AJ26" s="6">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>0</v>
+      </c>
+      <c r="B27" s="6">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6">
+        <v>1</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6">
+        <v>1</v>
+      </c>
+      <c r="V27" s="24"/>
+      <c r="W27" s="22">
+        <v>0</v>
+      </c>
+      <c r="X27" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V28" s="24"/>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V29" s="24"/>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B30" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="36"/>
+      <c r="G30" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="36"/>
+      <c r="L30" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" s="36"/>
+      <c r="V30" s="24"/>
+      <c r="X30" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y30" s="36"/>
+      <c r="AC30" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD30" s="36"/>
+      <c r="AH30" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI30" s="36"/>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="F31" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="K31" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="V31" s="24"/>
+      <c r="X31" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y31" s="36"/>
+      <c r="AC31" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD31" s="36"/>
+      <c r="AG31" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH31" s="35"/>
+      <c r="AI31" s="35"/>
+      <c r="AJ31" s="35"/>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <f>COS(J11)</f>
+        <v>1</v>
+      </c>
+      <c r="B32" s="6">
+        <f>-SIN(J11)*COS(K11)</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="6">
+        <f>SIN(J11)*SIN(K11)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="6">
+        <f>M11*COS(J11)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <f>COS(G9)*COS(G10)</f>
+        <v>1</v>
+      </c>
+      <c r="G32" s="6">
+        <f>COS(G9)*SIN(G10)*SIN(G11)-SIN(G9)*COS(G11)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="6">
+        <f>COS(G9)*SIN(G10)*COS(G11)+SIN(G9)*SIN(G11)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="6">
+        <f>F6</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="6">
+        <f t="array" ref="K32:N35">MMULT(A16:D19,F16:I19)</f>
+        <v>1</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0</v>
+      </c>
+      <c r="N32" s="6">
+        <v>23.5</v>
+      </c>
+      <c r="V32" s="24"/>
+      <c r="X32" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y32" s="6">
+        <f>ATAN2(AJ24,AJ25)</f>
+        <v>-1.0235158353455473E-18</v>
+      </c>
+      <c r="AC32" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD32" s="3">
+        <f>ABS(X38-M6)</f>
+        <v>575</v>
+      </c>
+      <c r="AG32" s="6">
+        <f>COS(AC6)</f>
+        <v>1</v>
+      </c>
+      <c r="AH32" s="6">
+        <f>-SIN(AC6)*COS(K6)</f>
+        <v>6.2697942212405134E-35</v>
+      </c>
+      <c r="AI32" s="6">
+        <f>SIN(AC6)*SIN(K6)</f>
+        <v>1.0235158353455473E-18</v>
+      </c>
+      <c r="AJ32" s="6">
+        <f>M6*COS(AC6)</f>
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <f>SIN(J11)</f>
+        <v>0</v>
+      </c>
+      <c r="B33" s="6">
+        <f>COS(J11)*COS(K11)</f>
+        <v>1</v>
+      </c>
+      <c r="C33" s="6">
+        <f>-COS(J11)*SIN(K11)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="6">
+        <f>M11*SIN(J11)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
+        <f>SIN(G9)*COS(G10)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="6">
+        <f>SIN(G9)*SIN(G10)*SIN(G11)+COS(G9)*COS(G11)</f>
+        <v>1</v>
+      </c>
+      <c r="H33" s="6">
+        <f>SIN(G9)*SIN(G10)*COS(G11)-COS(G9)*SIN(G11)</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6">
+        <f>F7</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0</v>
+      </c>
+      <c r="L33" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M33" s="6">
+        <v>1</v>
+      </c>
+      <c r="N33" s="6">
+        <v>0</v>
+      </c>
+      <c r="V33" s="24"/>
+      <c r="AC33" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD33" s="6">
+        <f>SQRT(AD32^2+AD34^2)</f>
+        <v>867.82774788548909</v>
+      </c>
+      <c r="AG33" s="6">
+        <f>SIN(AC6)</f>
+        <v>-1.0235158353455473E-18</v>
+      </c>
+      <c r="AH33" s="6">
+        <f>COS(AC6)*COS(K6)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AI33" s="6">
+        <f>-COS(AC6)*SIN(K6)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ33" s="6">
+        <f>M6*SIN(AC6)</f>
+        <v>-2.4052622130620362E-17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <v>0</v>
+      </c>
+      <c r="B34" s="6">
+        <f>SIN(K11)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="6">
+        <f>COS(K11)</f>
+        <v>1</v>
+      </c>
+      <c r="D34" s="6">
+        <f>L11</f>
+        <v>65</v>
+      </c>
+      <c r="F34" s="6">
+        <f>-SIN(G10)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="6">
+        <f>COS(G10)*SIN(G11)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="6">
+        <f>COS(G10)*COS(G11)</f>
+        <v>1</v>
+      </c>
+      <c r="I34" s="6">
+        <f>F8</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="M34" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="N34" s="6">
+        <v>191</v>
+      </c>
+      <c r="V34" s="24"/>
+      <c r="AC34" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD34" s="6">
+        <f>AJ26-L6</f>
+        <v>650</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <f>SIN(K6)</f>
+        <v>-1</v>
+      </c>
+      <c r="AI34" s="6">
+        <f>COS(K6)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AJ34" s="6">
+        <f>L6</f>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <v>0</v>
+      </c>
+      <c r="B35" s="6">
+        <v>0</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6">
+        <v>1</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6">
+        <v>0</v>
+      </c>
+      <c r="N35" s="6">
+        <v>1</v>
+      </c>
+      <c r="V35" s="24"/>
+      <c r="X35" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y35" s="36"/>
+      <c r="AC35" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD35" s="6">
+        <f>L9</f>
+        <v>575</v>
+      </c>
+      <c r="AG35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V36" s="24"/>
+      <c r="X36" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y36" s="35"/>
+      <c r="AC36" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD36" s="6">
+        <f>DEGREES(ATAN2(AD32,AD34))</f>
+        <v>48.503531644784459</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V37" s="24"/>
+      <c r="X37" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y37" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC37" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD37" s="14">
+        <f>DEGREES(ACOS((M7^2+AD33^2-AD35^2)/(2*M7*AD33)))</f>
+        <v>41.496468355215534</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B38" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="G38" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="H38" s="36"/>
+      <c r="L38" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="M38" s="36"/>
+      <c r="V38" s="24"/>
+      <c r="X38" s="6">
+        <f>(AJ24*COS(-Y32))-AJ25*SIN(-Y32)</f>
+        <v>598.5</v>
+      </c>
+      <c r="Y38" s="6">
+        <f>(AJ25*COS(-Y32))+(AJ24*SIN(-Y32))</f>
+        <v>0</v>
+      </c>
+      <c r="AC38" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD38" s="3">
+        <f>DEGREES(ACOS((M7^2+AD35^2-AD33^2)/(2*M7*AD35)))</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A39" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="F39" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="K39" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="V39" s="24"/>
+    </row>
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A40" s="6">
+        <f t="array" ref="A40:D43">MMULT(K32:N35,K16:N19)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="B40" s="6">
+        <v>1</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6">
+        <v>23.500000000000039</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="array" ref="F40:I43">MMULT(A40:D43,A24:D27)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="G40" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="H40" s="6">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6">
+        <v>23.500000000000039</v>
+      </c>
+      <c r="K40" s="6">
+        <f t="array" ref="K40:N43">MMULT(F40:I43,F24:I27)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="L40" s="6">
+        <v>-1</v>
+      </c>
+      <c r="M40" s="6">
+        <v>0</v>
+      </c>
+      <c r="N40" s="6">
+        <v>598.5</v>
+      </c>
+      <c r="V40" s="24"/>
+    </row>
+    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A41" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="B41" s="6">
+        <v>3.7524718414124473E-33</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-3.981732478453015E-14</v>
+      </c>
+      <c r="F41" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="I41" s="6">
+        <v>-3.981732478453015E-14</v>
+      </c>
+      <c r="K41" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="L41" s="6">
+        <v>0</v>
+      </c>
+      <c r="M41" s="6">
+        <v>1</v>
+      </c>
+      <c r="N41" s="6">
+        <v>-4.594306705907325E-15</v>
+      </c>
+      <c r="V41" s="24"/>
+      <c r="X41" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y41" s="36"/>
+      <c r="AC41" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD41" s="36"/>
+      <c r="AH41" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI41" s="36"/>
+    </row>
+    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A42" s="6">
+        <v>1</v>
+      </c>
+      <c r="B42" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="C42" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="D42" s="6">
+        <v>841</v>
+      </c>
+      <c r="F42" s="6">
+        <v>-1</v>
+      </c>
+      <c r="G42" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="H42" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="I42" s="6">
+        <v>841</v>
+      </c>
+      <c r="K42" s="6">
+        <v>-1</v>
+      </c>
+      <c r="L42" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="M42" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="N42" s="6">
+        <v>841</v>
+      </c>
+      <c r="V42" s="24"/>
+      <c r="W42" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="X42" s="35"/>
+      <c r="Y42" s="35"/>
+      <c r="Z42" s="35"/>
+      <c r="AB42" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC42" s="35"/>
+      <c r="AD42" s="35"/>
+      <c r="AE42" s="35"/>
+      <c r="AG42" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH42" s="35"/>
+      <c r="AI42" s="35"/>
+      <c r="AJ42" s="35"/>
+    </row>
+    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A43" s="6">
+        <v>0</v>
+      </c>
+      <c r="B43" s="6">
+        <v>0</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6">
+        <v>1</v>
+      </c>
+      <c r="K43" s="6">
+        <v>0</v>
+      </c>
+      <c r="L43" s="6">
+        <v>0</v>
+      </c>
+      <c r="M43" s="6">
+        <v>0</v>
+      </c>
+      <c r="N43" s="6">
+        <v>1</v>
+      </c>
+      <c r="V43" s="24"/>
+      <c r="W43" s="22">
+        <f>COS(AC7-RADIANS(90))</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="X43" s="6">
+        <f>-SIN(AC7-RADIANS(90))*COS(K7)</f>
+        <v>1</v>
+      </c>
+      <c r="Y43" s="6">
+        <f>SIN(AC7-RADIANS(90))*SIN(K7)</f>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="6">
+        <f>M7*COS(AC7-RADIANS(90))</f>
+        <v>3.981732478453015E-14</v>
+      </c>
+      <c r="AA43" s="18"/>
+      <c r="AB43" s="6">
+        <f>COS(AC8+RADIANS(180))</f>
+        <v>-1</v>
+      </c>
+      <c r="AC43" s="6">
+        <f>-SIN(AC8+RADIANS(180))*COS(K8)</f>
+        <v>-7.5049436828248946E-33</v>
+      </c>
+      <c r="AD43" s="6">
+        <f>SIN(AC8+RADIANS(180))*SIN(K8)</f>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="AE43" s="6">
+        <f>M8*COS(AC8+RADIANS(180))</f>
+        <v>0</v>
+      </c>
+      <c r="AF43" s="18"/>
+      <c r="AG43" s="6">
+        <f t="array" ref="AG43:AJ46">MMULT(AG32:AJ35,W43:Z46)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>1.0235158353455473E-18</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>23.500000000000039</v>
+      </c>
+    </row>
+    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V44" s="24"/>
+      <c r="W44" s="22">
+        <f>SIN(AC7-RADIANS(90))</f>
+        <v>-1</v>
+      </c>
+      <c r="X44" s="6">
+        <f>COS(AC7-RADIANS(90))*COS(K7)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="Y44" s="6">
+        <f>-COS(AC7-RADIANS(90))*SIN(K7)</f>
+        <v>0</v>
+      </c>
+      <c r="Z44" s="6">
+        <f>M7*SIN(AC7-RADIANS(90))</f>
+        <v>-650</v>
+      </c>
+      <c r="AA44" s="18"/>
+      <c r="AB44" s="6">
+        <f>SIN(AC8+RADIANS(180))</f>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="AC44" s="6">
+        <f>COS(AC8+RADIANS(180))*COS(K8)</f>
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="AD44" s="6">
+        <f>-COS(AC8+RADIANS(180))*SIN(K8)</f>
+        <v>1</v>
+      </c>
+      <c r="AE44" s="6">
+        <f>M8*SIN(AC8+RADIANS(180))</f>
+        <v>0</v>
+      </c>
+      <c r="AF44" s="18"/>
+      <c r="AG44" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="AH44" s="6">
+        <v>-1.0235158353455436E-18</v>
+      </c>
+      <c r="AI44" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ44" s="6">
+        <v>-3.9841377406660771E-14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="V45" s="24"/>
+      <c r="W45" s="22">
+        <v>0</v>
+      </c>
+      <c r="X45" s="6">
+        <f>SIN(K7)</f>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="6">
+        <f>COS(K7)</f>
+        <v>1</v>
+      </c>
+      <c r="Z45" s="6">
+        <f>L7</f>
+        <v>0</v>
+      </c>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="6">
+        <f>SIN(K8)</f>
+        <v>1</v>
+      </c>
+      <c r="AD45" s="6">
+        <f>COS(K8)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AE45" s="6">
+        <f>L8</f>
+        <v>0</v>
+      </c>
+      <c r="AF45" s="18"/>
+      <c r="AG45" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH45" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="AI45" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AJ45" s="6">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B46" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="36"/>
+      <c r="G46" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="36"/>
+      <c r="L46" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="M46" s="36"/>
+      <c r="V46" s="24"/>
+      <c r="W46" s="22">
+        <v>0</v>
+      </c>
+      <c r="X46" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="18"/>
+      <c r="AB46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF46" s="18"/>
+      <c r="AG46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A47" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="F47" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="K47" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="V47" s="24"/>
+    </row>
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
+        <f t="array" ref="A48:D51">MMULT(K40:N43,K24:N27)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="B48" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
+      <c r="D48" s="6">
+        <v>598.5</v>
+      </c>
+      <c r="F48" s="6">
+        <f t="array" ref="F48:I51">MMULT(A48:D51,A32:D35)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="G48" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="H48" s="6">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6">
+        <v>663.5</v>
+      </c>
+      <c r="K48" s="6">
+        <f t="array" ref="K48:N51">MMULT(F48:I51,F32:I35)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="L48" s="6">
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="M48" s="6">
+        <v>1</v>
+      </c>
+      <c r="N48" s="6">
+        <v>663.5</v>
+      </c>
+      <c r="V48" s="24"/>
+    </row>
+    <row r="49" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-4.594306705907325E-15</v>
+      </c>
+      <c r="F49" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="G49" s="6">
+        <v>1</v>
+      </c>
+      <c r="H49" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="I49" s="6">
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="K49" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="L49" s="6">
+        <v>1</v>
+      </c>
+      <c r="M49" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="N49" s="6">
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="V49" s="24"/>
+      <c r="X49" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y49" s="36"/>
+      <c r="AB49" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC49" s="36"/>
+      <c r="AD49" s="36"/>
+      <c r="AE49" s="36"/>
+      <c r="AG49" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH49" s="36"/>
+      <c r="AI49" s="36"/>
+      <c r="AJ49" s="36"/>
+    </row>
+    <row r="50" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <v>-1</v>
+      </c>
+      <c r="B50" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="C50" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="D50" s="6">
+        <v>841</v>
+      </c>
+      <c r="F50" s="6">
+        <v>-1</v>
+      </c>
+      <c r="G50" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="H50" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="I50" s="6">
+        <v>841</v>
+      </c>
+      <c r="K50" s="6">
+        <v>-1</v>
+      </c>
+      <c r="L50" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M50" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="N50" s="6">
+        <v>841</v>
+      </c>
+      <c r="V50" s="24"/>
+      <c r="W50" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="X50" s="35"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AB50" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC50" s="35"/>
+      <c r="AD50" s="35"/>
+      <c r="AE50" s="35"/>
+      <c r="AG50" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH50" s="35"/>
+      <c r="AI50" s="35"/>
+      <c r="AJ50" s="35"/>
+    </row>
+    <row r="51" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A51" s="6">
+        <v>0</v>
+      </c>
+      <c r="B51" s="6">
+        <v>0</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6">
+        <v>1</v>
+      </c>
+      <c r="K51" s="6">
+        <v>0</v>
+      </c>
+      <c r="L51" s="6">
+        <v>0</v>
+      </c>
+      <c r="M51" s="6">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6">
+        <v>1</v>
+      </c>
+      <c r="V51" s="24"/>
+      <c r="W51" s="22">
+        <f t="array" ref="W51:Z54">MMULT(AG43:AJ46,AB43:AE46)</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="X51" s="6">
+        <v>-6.0233906910085458E-17</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>23.500000000000039</v>
+      </c>
+      <c r="AA51" s="18"/>
+      <c r="AB51" s="6">
+        <f>W51</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AC51" s="6">
+        <f>W52</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AD51" s="6">
+        <f>W53</f>
+        <v>-1</v>
+      </c>
+      <c r="AE51" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF51" s="18"/>
+      <c r="AG51" s="6">
+        <f t="array" ref="AG51:AI53">MMULT(AB51:AD53,W24:Y26)</f>
+        <v>1</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>1.7941883724125684E-17</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>1.7941883724125678E-17</v>
+      </c>
+      <c r="AJ51" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="V52" s="24"/>
+      <c r="W52" s="22">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="X52" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="6">
+        <v>6.0233906910085445E-17</v>
+      </c>
+      <c r="Z52" s="6">
+        <v>-3.9841377406660771E-14</v>
+      </c>
+      <c r="AA52" s="18"/>
+      <c r="AB52" s="6">
+        <f>X51</f>
+        <v>-6.0233906910085458E-17</v>
+      </c>
+      <c r="AC52" s="6">
+        <f>X52</f>
+        <v>1</v>
+      </c>
+      <c r="AD52" s="6">
+        <f>X53</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AE52" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF52" s="18"/>
+      <c r="AG52" s="6">
+        <v>-1.7941883724125684E-17</v>
+      </c>
+      <c r="AH52" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>-6.0233906910085458E-17</v>
+      </c>
+      <c r="AJ52" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="V53" s="24"/>
+      <c r="W53" s="22">
+        <v>-1</v>
+      </c>
+      <c r="X53" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>841</v>
+      </c>
+      <c r="AA53" s="18"/>
+      <c r="AB53" s="6">
+        <f>Y51</f>
+        <v>1</v>
+      </c>
+      <c r="AC53" s="6">
+        <f>Y52</f>
+        <v>6.0233906910085445E-17</v>
+      </c>
+      <c r="AD53" s="6">
+        <f>Y53</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="AE53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF53" s="18"/>
+      <c r="AG53" s="6">
+        <v>-1.7941883724125678E-17</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>6.0233906910085445E-17</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ53" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="V54" s="24"/>
+      <c r="W54" s="22">
+        <v>0</v>
+      </c>
+      <c r="X54" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="18"/>
+      <c r="AB54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF54" s="18"/>
+      <c r="AG54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ54" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="V55" s="24"/>
+      <c r="AE55" s="19"/>
+    </row>
+    <row r="56" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A56" s="46"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
+      <c r="L56" s="46"/>
+      <c r="M56" s="46"/>
+      <c r="N56" s="46"/>
+      <c r="O56" s="46"/>
+      <c r="P56" s="46"/>
+      <c r="Q56" s="46"/>
+      <c r="R56" s="46"/>
+      <c r="S56" s="46"/>
+      <c r="T56" s="46"/>
+      <c r="U56" s="46"/>
+      <c r="V56" s="46"/>
+      <c r="W56" s="46"/>
+      <c r="X56" s="46"/>
+      <c r="Y56" s="46"/>
+      <c r="Z56" s="46"/>
+      <c r="AA56" s="46"/>
+      <c r="AB56" s="46"/>
+      <c r="AC56" s="46"/>
+      <c r="AD56" s="46"/>
+      <c r="AE56" s="46"/>
+      <c r="AF56" s="46"/>
+      <c r="AG56" s="46"/>
+      <c r="AH56" s="46"/>
+      <c r="AI56" s="46"/>
+      <c r="AJ56" s="46"/>
+      <c r="AK56" s="46"/>
+      <c r="AL56" s="46"/>
+      <c r="AM56" s="46"/>
+      <c r="AN56" s="46"/>
+      <c r="AO56" s="46"/>
+      <c r="AP56" s="46"/>
+      <c r="AQ56" s="46"/>
+      <c r="AR56" s="46"/>
+      <c r="AS56" s="46"/>
+    </row>
+    <row r="57" spans="1:45" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="B57" s="42"/>
+      <c r="C57" s="42"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="42"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
+      <c r="L57" s="42"/>
+      <c r="M57" s="42"/>
+      <c r="N57" s="42"/>
+      <c r="O57" s="42"/>
+      <c r="P57" s="42"/>
+      <c r="Q57" s="42"/>
+      <c r="R57" s="42"/>
+      <c r="S57" s="42"/>
+      <c r="T57" s="42"/>
+      <c r="U57" s="42"/>
+      <c r="V57" s="24"/>
+      <c r="W57" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="X57" s="42"/>
+      <c r="Y57" s="42"/>
+      <c r="Z57" s="42"/>
+      <c r="AA57" s="42"/>
+      <c r="AB57" s="42"/>
+      <c r="AC57" s="42"/>
+      <c r="AD57" s="42"/>
+      <c r="AE57" s="42"/>
+      <c r="AF57" s="42"/>
+      <c r="AG57" s="42"/>
+      <c r="AH57" s="42"/>
+      <c r="AI57" s="42"/>
+      <c r="AJ57" s="42"/>
+      <c r="AK57" s="42"/>
+      <c r="AL57" s="42"/>
+      <c r="AM57" s="42"/>
+      <c r="AN57" s="42"/>
+      <c r="AO57" s="42"/>
+      <c r="AP57" s="42"/>
+      <c r="AQ57" s="42"/>
+      <c r="AR57" s="42"/>
+      <c r="AS57" s="42"/>
+    </row>
+    <row r="58" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="43"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+      <c r="L58" s="43"/>
+      <c r="M58" s="43"/>
+      <c r="N58" s="43"/>
+      <c r="O58" s="43"/>
+      <c r="P58" s="43"/>
+      <c r="Q58" s="43"/>
+      <c r="R58" s="43"/>
+      <c r="S58" s="43"/>
+      <c r="T58" s="43"/>
+      <c r="U58" s="43"/>
+      <c r="V58" s="24"/>
+      <c r="AA58" s="16"/>
+      <c r="AB58" s="16"/>
+    </row>
+    <row r="59" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A59" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="40"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="F59" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="K59" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="L59" s="34"/>
+      <c r="M59" s="34"/>
+      <c r="N59" s="34"/>
+      <c r="O59" s="34"/>
+      <c r="P59" s="34"/>
+      <c r="V59" s="24"/>
+    </row>
+    <row r="60" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="6">
+        <f t="shared" ref="B60:B62" si="4">M32</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D60" s="6">
+        <f>M40</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H60" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="I60" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="K60" s="6">
+        <f>H61</f>
+        <v>650</v>
+      </c>
+      <c r="L60" s="6">
+        <f>H64</f>
+        <v>-2.4015819785039663E-30</v>
+      </c>
+      <c r="M60" s="6">
+        <f>H67</f>
+        <v>-2.4015819785039663E-30</v>
+      </c>
+      <c r="N60" s="26">
+        <f>H70</f>
+        <v>-2.4391066969180907E-31</v>
+      </c>
+      <c r="O60" s="6">
+        <f>H73</f>
+        <v>-2.4391066969180907E-31</v>
+      </c>
+      <c r="P60" s="6">
+        <f>H76</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="24"/>
+    </row>
+    <row r="61" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A61" s="38"/>
+      <c r="B61" s="6">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="C61" s="38"/>
+      <c r="D61" s="6">
+        <f>M41</f>
+        <v>1</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="6">
+        <f>N48-B72</f>
+        <v>640</v>
+      </c>
+      <c r="H61" s="26">
+        <f>B61*G63-B62*G62</f>
+        <v>650</v>
+      </c>
+      <c r="I61" s="26">
+        <f t="shared" ref="I61:I69" si="5">B60</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="6">
+        <f>H62</f>
+        <v>3.920475055707584E-14</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0</v>
+      </c>
+      <c r="M61" s="6">
+        <f>H68</f>
+        <v>3.920475055707584E-14</v>
+      </c>
+      <c r="N61" s="26">
+        <f>H71</f>
+        <v>3.981732478453015E-15</v>
+      </c>
+      <c r="O61" s="6">
+        <f>H74</f>
+        <v>3.981732478453015E-15</v>
+      </c>
+      <c r="P61" s="6">
+        <f>H77</f>
+        <v>0</v>
+      </c>
+      <c r="V61" s="24"/>
+    </row>
+    <row r="62" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A62" s="39"/>
+      <c r="B62" s="6">
+        <f t="shared" si="4"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="C62" s="39"/>
+      <c r="D62" s="6">
+        <f>M42</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="F62" s="38"/>
+      <c r="G62" s="6">
+        <f>N49-B73</f>
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="H62" s="6">
+        <f>B62*G61-B60*G63</f>
+        <v>3.920475055707584E-14</v>
+      </c>
+      <c r="I62" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K62" s="6">
+        <f>H63</f>
+        <v>-640</v>
+      </c>
+      <c r="L62" s="6">
+        <f>H66</f>
+        <v>-640</v>
+      </c>
+      <c r="M62" s="6">
+        <f>H69</f>
+        <v>0</v>
+      </c>
+      <c r="N62" s="26">
+        <f>H72</f>
+        <v>-65</v>
+      </c>
+      <c r="O62" s="6">
+        <f>H75</f>
+        <v>0</v>
+      </c>
+      <c r="P62" s="6">
+        <f>H78</f>
+        <v>0</v>
+      </c>
+      <c r="V62" s="24"/>
+    </row>
+    <row r="63" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A63" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B63" s="6">
+        <f>C40</f>
+        <v>0</v>
+      </c>
+      <c r="C63" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" s="6">
+        <f>C48</f>
+        <v>1</v>
+      </c>
+      <c r="F63" s="39"/>
+      <c r="G63" s="6">
+        <f>N50-B74</f>
+        <v>650</v>
+      </c>
+      <c r="H63" s="6">
+        <f>B60*G62-B61*G61</f>
+        <v>-640</v>
+      </c>
+      <c r="I63" s="6">
+        <f t="shared" si="5"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="K63" s="6">
+        <f>I61</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="6">
+        <f>I64</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="6">
+        <f>I67</f>
+        <v>1</v>
+      </c>
+      <c r="N63" s="6">
+        <f>I70</f>
+        <v>0</v>
+      </c>
+      <c r="O63" s="6">
+        <f>I73</f>
+        <v>1</v>
+      </c>
+      <c r="P63" s="6">
+        <f>I76</f>
+        <v>1</v>
+      </c>
+      <c r="V63" s="24"/>
+    </row>
+    <row r="64" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="38"/>
+      <c r="B64" s="6">
+        <f>C41</f>
+        <v>1</v>
+      </c>
+      <c r="C64" s="38"/>
+      <c r="D64" s="6">
+        <f>C49</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="F64" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" s="6">
+        <f>N48-B75</f>
+        <v>640</v>
+      </c>
+      <c r="H64" s="26">
+        <f>B64*G66-B65*G65</f>
+        <v>-2.4015819785039663E-30</v>
+      </c>
+      <c r="I64" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K64" s="6">
+        <f>I62</f>
+        <v>1</v>
+      </c>
+      <c r="L64" s="6">
+        <f>I65</f>
+        <v>1</v>
+      </c>
+      <c r="M64" s="6">
+        <f>I68</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="N64" s="6">
+        <f>I71</f>
+        <v>1</v>
+      </c>
+      <c r="O64" s="6">
+        <f>I74</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="P64" s="6">
+        <f>I77</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="V64" s="24"/>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A65" s="39"/>
+      <c r="B65" s="6">
+        <f>C42</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="C65" s="39"/>
+      <c r="D65" s="6">
+        <f>C50</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="F65" s="38"/>
+      <c r="G65" s="6">
+        <f>N49-B76</f>
+        <v>3.920475055707584E-14</v>
+      </c>
+      <c r="H65" s="6">
+        <f>B65*G64-B63*G66</f>
+        <v>3.920475055707584E-14</v>
+      </c>
+      <c r="I65" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K65" s="6">
+        <f>I63</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="L65" s="6">
+        <f>I66</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M65" s="6">
+        <f>I69</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="N65" s="6">
+        <f>I72</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="O65" s="6">
+        <f>I75</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="P65" s="6">
+        <f>I78</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="V65" s="24"/>
+    </row>
+    <row r="66" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" s="6">
+        <f>H40</f>
+        <v>1</v>
+      </c>
+      <c r="C66" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="6">
+        <f>H48</f>
+        <v>1</v>
+      </c>
+      <c r="F66" s="39"/>
+      <c r="G66" s="6">
+        <f>N50-B77</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="6">
+        <f>B63*G65-B64*G64</f>
+        <v>-640</v>
+      </c>
+      <c r="I66" s="6">
+        <f t="shared" si="5"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="V66" s="24"/>
+    </row>
+    <row r="67" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="38"/>
+      <c r="B67" s="6">
+        <f>H41</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="C67" s="38"/>
+      <c r="D67" s="6">
+        <f>H49</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="F67" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="6">
+        <f>N48-B78</f>
+        <v>640</v>
+      </c>
+      <c r="H67" s="26">
+        <f>B67*G69-B68*G68</f>
+        <v>-2.4015819785039663E-30</v>
+      </c>
+      <c r="I67" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="V67" s="24"/>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A68" s="39"/>
+      <c r="B68" s="6">
+        <f>H42</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="C68" s="39"/>
+      <c r="D68" s="6">
+        <f>H50</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="F68" s="38"/>
+      <c r="G68" s="6">
+        <f>N49-B79</f>
+        <v>3.920475055707584E-14</v>
+      </c>
+      <c r="H68" s="6">
+        <f>B68*G67-B66*G69</f>
+        <v>3.920475055707584E-14</v>
+      </c>
+      <c r="I68" s="6">
+        <f t="shared" si="5"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M68" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="N68" s="34"/>
+      <c r="V68" s="24"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F69" s="39"/>
+      <c r="G69" s="6">
+        <f>N50-B80</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="6">
+        <f>B66*G68-B67*G67</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="6">
+        <f t="shared" si="5"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M69" s="28" t="str">
+        <f>IF(N69=0, "S", "N")</f>
+        <v>S</v>
+      </c>
+      <c r="N69" s="17">
+        <f>MDETERM(K60:P65)</f>
+        <v>0</v>
+      </c>
+      <c r="V69" s="24"/>
+    </row>
+    <row r="70" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F70" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="6">
+        <f>N48-D72</f>
+        <v>65</v>
+      </c>
+      <c r="H70" s="26">
+        <f>D61*G72-D62*G71</f>
+        <v>-2.4391066969180907E-31</v>
+      </c>
+      <c r="I70" s="6">
+        <f t="shared" ref="I70:I78" si="6">D60</f>
+        <v>0</v>
+      </c>
+      <c r="V70" s="24"/>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A71" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="6">
+        <f>N49-D73</f>
+        <v>3.981732478453015E-15</v>
+      </c>
+      <c r="H71" s="6">
+        <f>D62*G70-D60*G72</f>
+        <v>3.981732478453015E-15</v>
+      </c>
+      <c r="I71" s="6">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="V71" s="24"/>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A72" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="6">
+        <f t="shared" ref="B72:B74" si="7">N32</f>
+        <v>23.5</v>
+      </c>
+      <c r="C72" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="6">
+        <f t="shared" ref="D72:D74" si="8">N40</f>
+        <v>598.5</v>
+      </c>
+      <c r="F72" s="39"/>
+      <c r="G72" s="6">
+        <f>N50-D74</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="6">
+        <f>D60*G71-D61*G70</f>
+        <v>-65</v>
+      </c>
+      <c r="I72" s="6">
+        <f t="shared" si="6"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="V72" s="24"/>
+    </row>
+    <row r="73" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="38"/>
+      <c r="B73" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="38"/>
+      <c r="D73" s="6">
+        <f t="shared" si="8"/>
+        <v>-4.594306705907325E-15</v>
+      </c>
+      <c r="F73" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G73" s="6">
+        <f>N48-D75</f>
+        <v>65</v>
+      </c>
+      <c r="H73" s="26">
+        <f>D64*G75-D65*G74</f>
+        <v>-2.4391066969180907E-31</v>
+      </c>
+      <c r="I73" s="6">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="V73" s="24"/>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A74" s="39"/>
+      <c r="B74" s="6">
+        <f t="shared" si="7"/>
+        <v>191</v>
+      </c>
+      <c r="C74" s="39"/>
+      <c r="D74" s="6">
+        <f t="shared" si="8"/>
+        <v>841</v>
+      </c>
+      <c r="F74" s="38"/>
+      <c r="G74" s="6">
+        <f>N49-D76</f>
+        <v>3.981732478453015E-15</v>
+      </c>
+      <c r="H74" s="6">
+        <f>D65*G73-D63*G75</f>
+        <v>3.981732478453015E-15</v>
+      </c>
+      <c r="I74" s="6">
+        <f t="shared" si="6"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="O74"/>
+      <c r="V74" s="24"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A75" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" s="6">
+        <f t="shared" ref="B75:B77" si="9">D40</f>
+        <v>23.500000000000039</v>
+      </c>
+      <c r="C75" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" s="6">
+        <f t="shared" ref="D75:D77" si="10">D48</f>
+        <v>598.5</v>
+      </c>
+      <c r="F75" s="39"/>
+      <c r="G75" s="6">
+        <f>N50-D77</f>
+        <v>0</v>
+      </c>
+      <c r="H75" s="6">
+        <f>D63*G74-D64*G73</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="6">
+        <f t="shared" si="6"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="V75" s="24"/>
+    </row>
+    <row r="76" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="38"/>
+      <c r="B76" s="6">
+        <f t="shared" si="9"/>
+        <v>-3.981732478453015E-14</v>
+      </c>
+      <c r="C76" s="38"/>
+      <c r="D76" s="6">
+        <f t="shared" si="10"/>
+        <v>-4.594306705907325E-15</v>
+      </c>
+      <c r="F76" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="6">
+        <f>N48-D78</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="26">
+        <f>D67*G78-D68*G77</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="6">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="R76"/>
+      <c r="V76" s="24"/>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A77" s="39"/>
+      <c r="B77" s="6">
+        <f t="shared" si="9"/>
+        <v>841</v>
+      </c>
+      <c r="C77" s="39"/>
+      <c r="D77" s="6">
+        <f t="shared" si="10"/>
+        <v>841</v>
+      </c>
+      <c r="F77" s="38"/>
+      <c r="G77" s="6">
+        <f>N49-D79</f>
+        <v>0</v>
+      </c>
+      <c r="H77" s="6">
+        <f>D68*G76-D66*G78</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="6">
+        <f t="shared" si="6"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="V77" s="24"/>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A78" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="6">
+        <f t="shared" ref="B78:B80" si="11">I40</f>
+        <v>23.500000000000039</v>
+      </c>
+      <c r="C78" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D78" s="6">
+        <f t="shared" ref="D78:D80" si="12">I48</f>
+        <v>663.5</v>
+      </c>
+      <c r="F78" s="39"/>
+      <c r="G78" s="6">
+        <f>N50-D80</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="6">
+        <f>D66*G77-D67*G76</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="6">
+        <f t="shared" si="6"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="V78" s="24"/>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A79" s="38"/>
+      <c r="B79" s="6">
+        <f t="shared" si="11"/>
+        <v>-3.981732478453015E-14</v>
+      </c>
+      <c r="C79" s="38"/>
+      <c r="D79" s="6">
+        <f t="shared" si="12"/>
+        <v>-6.1257422745431001E-16</v>
+      </c>
+      <c r="V79" s="24"/>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A80" s="39"/>
+      <c r="B80" s="6">
+        <f t="shared" si="11"/>
+        <v>841</v>
+      </c>
+      <c r="C80" s="39"/>
+      <c r="D80" s="6">
+        <f t="shared" si="12"/>
+        <v>841</v>
+      </c>
+      <c r="V80" s="24"/>
+    </row>
+    <row r="81" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V81" s="24"/>
+    </row>
+    <row r="82" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V82" s="24"/>
+    </row>
+    <row r="83" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V83" s="24"/>
     </row>
   </sheetData>
+  <mergeCells count="117">
+    <mergeCell ref="AH14:AI14"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="AB15:AE15"/>
+    <mergeCell ref="AG15:AJ15"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="AC30:AD30"/>
+    <mergeCell ref="AG23:AJ23"/>
+    <mergeCell ref="W15:Z15"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="AB23:AE23"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="W1:AS1"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="W50:Z50"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="AB42:AE42"/>
+    <mergeCell ref="AH41:AI41"/>
+    <mergeCell ref="X49:Y49"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="AG31:AJ31"/>
+    <mergeCell ref="W42:Z42"/>
+    <mergeCell ref="AH30:AI30"/>
+    <mergeCell ref="X41:Y41"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A57:U57"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="W2:AS2"/>
+    <mergeCell ref="A58:U58"/>
+    <mergeCell ref="AG49:AJ49"/>
+    <mergeCell ref="AG50:AJ50"/>
+    <mergeCell ref="AB49:AE49"/>
+    <mergeCell ref="AB50:AE50"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="W57:AS57"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A56:AS56"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="K47:N47"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="F70:F72"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="F67:F69"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="K59:P59"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="A78:A80"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="K9" formula="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Breakdown/Excel/Arm Info.xlsx
+++ b/Breakdown/Excel/Arm Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Udin\Kuliah\7. TUGAS AKHIR\Arm Manipulator\Breakdown\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9080F07-A07B-4879-BD58-9D4C266A8DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5B17B5-40CF-41D7-8AD5-40BAFE1781D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{313879A8-645A-4312-965B-79C9BD650931}"/>
   </bookViews>
@@ -843,13 +843,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -861,64 +906,19 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1219,7 +1219,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25228467" y="673704"/>
-          <a:ext cx="1881042" cy="1631346"/>
+          <a:ext cx="1892472" cy="1638966"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2637,195 +2637,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
       <c r="V1" s="27"/>
-      <c r="W1" s="42" t="s">
+      <c r="W1" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="42"/>
-      <c r="AH1" s="42"/>
-      <c r="AI1" s="42"/>
-      <c r="AJ1" s="42"/>
-      <c r="AK1" s="42"/>
-      <c r="AL1" s="42"/>
-      <c r="AM1" s="42"/>
-      <c r="AN1" s="42"/>
-      <c r="AO1" s="42"/>
-      <c r="AP1" s="42"/>
-      <c r="AQ1" s="42"/>
-      <c r="AR1" s="42"/>
-      <c r="AS1" s="42"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="49"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
     </row>
     <row r="2" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
       <c r="V2" s="24"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="43"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="43"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43"/>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="43"/>
-      <c r="AS2" s="43"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
     </row>
     <row r="3" spans="1:45" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="I3" s="44" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="I3" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="O3" s="44" t="s">
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="O3" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
       <c r="V3" s="24"/>
-      <c r="W3" s="44" t="s">
+      <c r="W3" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="AA3" s="44" t="s">
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="AA3" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="AB3" s="44"/>
-      <c r="AC3" s="44"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
     </row>
     <row r="4" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="55" t="s">
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="G4" s="57"/>
-      <c r="I4" s="47" t="s">
+      <c r="F4" s="51"/>
+      <c r="G4" s="45"/>
+      <c r="I4" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="L4" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="48" t="s">
+      <c r="M4" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="53" t="s">
+      <c r="O4" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="45" t="s">
+      <c r="P4" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="45" t="s">
+      <c r="Q4" s="41" t="s">
         <v>27</v>
       </c>
       <c r="V4" s="24"/>
-      <c r="W4" s="58" t="s">
+      <c r="W4" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="X4" s="53" t="s">
+      <c r="X4" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="Y4" s="53" t="s">
+      <c r="Y4" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="AA4" s="53" t="s">
+      <c r="AA4" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="AB4" s="55" t="s">
+      <c r="AB4" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="AC4" s="57"/>
+      <c r="AC4" s="45"/>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A5" s="54"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="8" t="s">
         <v>90</v>
       </c>
@@ -2844,19 +2844,19 @@
       <c r="G5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="47"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
       <c r="V5" s="24"/>
-      <c r="W5" s="59"/>
-      <c r="X5" s="54"/>
-      <c r="Y5" s="54"/>
-      <c r="AA5" s="54"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="40"/>
+      <c r="AA5" s="40"/>
       <c r="AB5" s="10" t="s">
         <v>30</v>
       </c>
@@ -2884,7 +2884,7 @@
       <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="46" t="s">
         <v>52</v>
       </c>
       <c r="I6" s="9">
@@ -2909,9 +2909,9 @@
       </c>
       <c r="P6" s="6">
         <f>N48</f>
-        <v>663.5</v>
-      </c>
-      <c r="Q6" s="50" t="s">
+        <v>598.5</v>
+      </c>
+      <c r="Q6" s="46" t="s">
         <v>52</v>
       </c>
       <c r="V6" s="24"/>
@@ -2919,10 +2919,9 @@
         <v>43</v>
       </c>
       <c r="X6" s="6">
-        <f t="shared" ref="X6:X11" si="0">P6</f>
-        <v>663.5</v>
-      </c>
-      <c r="Y6" s="50" t="s">
+        <v>598.5</v>
+      </c>
+      <c r="Y6" s="46" t="s">
         <v>52</v>
       </c>
       <c r="AA6" s="8" t="s">
@@ -2930,11 +2929,11 @@
       </c>
       <c r="AB6" s="6">
         <f>DEGREES(AC6)</f>
-        <v>-5.8643137630106747E-17</v>
+        <v>-7.6236078919138748E-16</v>
       </c>
       <c r="AC6" s="6">
         <f>Y32</f>
-        <v>-1.0235158353455473E-18</v>
+        <v>-1.3305705859492111E-17</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.3">
@@ -2957,7 +2956,7 @@
       <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="G7" s="51"/>
+      <c r="G7" s="47"/>
       <c r="I7" s="9">
         <v>2</v>
       </c>
@@ -2980,18 +2979,17 @@
       </c>
       <c r="P7" s="6">
         <f>N49</f>
-        <v>-6.1257422745431001E-16</v>
-      </c>
-      <c r="Q7" s="51"/>
+        <v>3.369158250998705E-15</v>
+      </c>
+      <c r="Q7" s="47"/>
       <c r="V7" s="24"/>
       <c r="W7" s="21" t="s">
         <v>44</v>
       </c>
       <c r="X7" s="6">
-        <f t="shared" si="0"/>
-        <v>-6.1257422745431001E-16</v>
-      </c>
-      <c r="Y7" s="51"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="47"/>
       <c r="AA7" s="8" t="s">
         <v>4</v>
       </c>
@@ -3024,7 +3022,7 @@
       <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="G8" s="52"/>
+      <c r="G8" s="48"/>
       <c r="I8" s="9">
         <v>3</v>
       </c>
@@ -3047,18 +3045,17 @@
       </c>
       <c r="P8" s="6">
         <f>N50</f>
-        <v>841</v>
-      </c>
-      <c r="Q8" s="52"/>
+        <v>776</v>
+      </c>
+      <c r="Q8" s="48"/>
       <c r="V8" s="24"/>
       <c r="W8" s="21" t="s">
         <v>45</v>
       </c>
       <c r="X8" s="6">
-        <f t="shared" si="0"/>
-        <v>841</v>
-      </c>
-      <c r="Y8" s="52"/>
+        <v>776</v>
+      </c>
+      <c r="Y8" s="48"/>
       <c r="AA8" s="8" t="s">
         <v>5</v>
       </c>
@@ -3082,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="6">
-        <f t="shared" ref="D9:D11" si="1">RADIANS(C9)</f>
+        <f t="shared" ref="D9:D11" si="0">RADIANS(C9)</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -3117,34 +3114,34 @@
       </c>
       <c r="P9" s="6">
         <f>DEGREES(Q9)</f>
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="Q9" s="6">
         <f>ATAN2(K48/COS(Q10),K49/COS(Q10))</f>
-        <v>0.78539816339744828</v>
+        <v>3.1415926535897931</v>
       </c>
       <c r="V9" s="24"/>
       <c r="W9" s="11" t="s">
         <v>47</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" si="0"/>
-        <v>45</v>
+        <f>P9</f>
+        <v>180</v>
       </c>
       <c r="Y9" s="6">
         <f>RADIANS(X9)</f>
-        <v>0.78539816339744828</v>
+        <v>3.1415926535897931</v>
       </c>
       <c r="AA9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="AB9" s="6">
         <f>DEGREES(AC9)</f>
-        <v>106.58722401468049</v>
+        <v>3.5097917871618874E-15</v>
       </c>
       <c r="AC9" s="6">
         <f>IF(AC10&gt;0, ATAN2(AI51,AI52),  ATAN2(-AI51,-AI52))</f>
-        <v>1.8602979996169433</v>
+        <v>6.1257422745430976E-17</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.3">
@@ -3155,11 +3152,11 @@
         <v>93</v>
       </c>
       <c r="C10" s="6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D10" s="6">
         <f>RADIANS(C10)</f>
-        <v>0</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>48</v>
@@ -3176,7 +3173,7 @@
       </c>
       <c r="J10" s="6">
         <f>D10</f>
-        <v>0</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="K10" s="6">
         <f>RADIANS(90)</f>
@@ -3193,34 +3190,34 @@
       </c>
       <c r="P10" s="6">
         <f>DEGREES(Q10)</f>
-        <v>90</v>
+        <v>7.0195835743237771E-15</v>
       </c>
       <c r="Q10" s="6">
         <f>ATAN2(SQRT(L50^2 + M50^2), -K50)</f>
-        <v>1.5707963267948966</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="V10" s="24"/>
       <c r="W10" s="11" t="s">
         <v>48</v>
       </c>
       <c r="X10" s="6">
-        <f t="shared" si="0"/>
-        <v>90</v>
+        <f>P10</f>
+        <v>7.0195835743237771E-15</v>
       </c>
       <c r="Y10" s="6">
-        <f t="shared" ref="Y10:Y11" si="2">RADIANS(X10)</f>
-        <v>1.5707963267948966</v>
+        <f t="shared" ref="Y10:Y11" si="1">RADIANS(X10)</f>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="AA10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="AB10" s="6">
         <f>DEGREES(AC10)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AC10" s="6">
         <f>IF(C10&gt;0,ATAN2(AI53,SQRT(1-AI53^2)), ATAN2(AI53,-SQRT(1-AI53^2)))</f>
-        <v>0</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.3">
@@ -3234,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -3269,34 +3266,34 @@
       </c>
       <c r="P11" s="6">
         <f>DEGREES(Q11)</f>
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="Q11" s="6">
         <f>ATAN2(M50/COS(Q10),L50/COS(Q10))</f>
-        <v>0.78539816339744828</v>
+        <v>3.1415926535897931</v>
       </c>
       <c r="V11" s="24"/>
       <c r="W11" s="11" t="s">
         <v>46</v>
       </c>
       <c r="X11" s="6">
-        <f t="shared" si="0"/>
-        <v>45</v>
+        <f>P11</f>
+        <v>180</v>
       </c>
       <c r="Y11" s="6">
-        <f t="shared" si="2"/>
-        <v>0.78539816339744828</v>
+        <f t="shared" si="1"/>
+        <v>3.1415926535897931</v>
       </c>
       <c r="AA11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="AB11" s="6">
         <f>DEGREES(AC11)</f>
-        <v>-106.58722401468049</v>
+        <v>9.7670145722942758E-15</v>
       </c>
       <c r="AC11" s="6">
         <f>IF(AC10&gt;0, ATAN2(-AG53,AH53), ATAN2(AG53,-AH53))</f>
-        <v>-1.8602979996169433</v>
+        <v>1.7046656237680085E-16</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.3">
@@ -3308,31 +3305,31 @@
       <c r="V13" s="24"/>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="G14" s="36" t="s">
+      <c r="C14" s="34"/>
+      <c r="G14" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="L14" s="36" t="s">
+      <c r="H14" s="34"/>
+      <c r="L14" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="M14" s="36"/>
+      <c r="M14" s="34"/>
       <c r="V14" s="24"/>
-      <c r="X14" s="36" t="s">
+      <c r="X14" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="Y14" s="36"/>
-      <c r="AC14" s="36" t="s">
+      <c r="Y14" s="34"/>
+      <c r="AC14" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="AD14" s="36"/>
-      <c r="AH14" s="36" t="s">
+      <c r="AD14" s="34"/>
+      <c r="AH14" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="36"/>
+      <c r="AI14" s="34"/>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
@@ -3421,35 +3418,35 @@
       <c r="V16" s="24"/>
       <c r="W16" s="22">
         <f>COS(RADIANS(X9))*COS(RADIANS(X10))</f>
-        <v>4.3315539021305322E-17</v>
+        <v>-1</v>
       </c>
       <c r="X16" s="6">
         <f>COS(RADIANS(X9))*SIN(RADIANS(X10))*SIN(RADIANS(X11))-SIN(RADIANS(X9))*COS(RADIANS(X11))</f>
-        <v>0</v>
+        <v>1.2251484549086198E-16</v>
       </c>
       <c r="Y16" s="6">
         <f>COS(RADIANS(X9))*SIN(RADIANS(X10))*COS(RADIANS(X11))+SIN(RADIANS(X9))*SIN(RADIANS(X11))</f>
-        <v>1</v>
+        <v>1.2251484549086203E-16</v>
       </c>
       <c r="Z16" s="6">
         <f>X6</f>
-        <v>663.5</v>
+        <v>598.5</v>
       </c>
       <c r="AA16" s="18"/>
       <c r="AB16" s="6">
-        <f t="shared" ref="AB16:AE19" si="3">F32</f>
+        <f t="shared" ref="AB16:AE19" si="2">F32</f>
         <v>1</v>
       </c>
       <c r="AC16" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD16" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE16" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF16" s="18"/>
@@ -3518,7 +3515,7 @@
       <c r="V17" s="24"/>
       <c r="W17" s="22">
         <f>SIN(RADIANS(X9))*COS(RADIANS(X10))</f>
-        <v>4.3315539021305316E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="X17" s="6">
         <f>SIN(RADIANS(X9))*SIN(RADIANS(X10))*SIN(RADIANS(X11))+COS(RADIANS(X9))*COS(RADIANS(X11))</f>
@@ -3526,27 +3523,27 @@
       </c>
       <c r="Y17" s="6">
         <f>SIN(RADIANS(X9))*SIN(RADIANS(X10))*COS(RADIANS(X11))-COS(RADIANS(X9))*SIN(RADIANS(X11))</f>
-        <v>0</v>
+        <v>1.2251484549086198E-16</v>
       </c>
       <c r="Z17" s="6">
         <f>X7</f>
-        <v>-6.1257422745431001E-16</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="18"/>
       <c r="AB17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AD17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF17" s="18"/>
@@ -3613,35 +3610,35 @@
       <c r="V18" s="24"/>
       <c r="W18" s="22">
         <f>-SIN(RADIANS(X10))</f>
-        <v>-1</v>
+        <v>-1.22514845490862E-16</v>
       </c>
       <c r="X18" s="6">
         <f>COS(RADIANS(X10))*SIN(RADIANS(X11))</f>
-        <v>4.3315539021305316E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="Y18" s="6">
         <f>COS(RADIANS(X10))*COS(RADIANS(X11))</f>
-        <v>4.3315539021305322E-17</v>
+        <v>-1</v>
       </c>
       <c r="Z18" s="6">
         <f>X8</f>
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="AA18" s="18"/>
       <c r="AB18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AE18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF18" s="18"/>
@@ -3714,19 +3711,19 @@
       </c>
       <c r="AA19" s="18"/>
       <c r="AB19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF19" s="18"/>
@@ -3751,31 +3748,31 @@
       <c r="V21" s="24"/>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="G22" s="36" t="s">
+      <c r="C22" s="34"/>
+      <c r="G22" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="L22" s="36" t="s">
+      <c r="H22" s="34"/>
+      <c r="L22" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="M22" s="36"/>
+      <c r="M22" s="34"/>
       <c r="V22" s="24"/>
-      <c r="X22" s="36" t="s">
+      <c r="X22" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="Y22" s="36"/>
-      <c r="AC22" s="36" t="s">
+      <c r="Y22" s="34"/>
+      <c r="AC22" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="AD22" s="36"/>
-      <c r="AH22" s="36" t="s">
+      <c r="AD22" s="34"/>
+      <c r="AH22" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="AI22" s="36"/>
+      <c r="AI22" s="34"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
@@ -3851,15 +3848,15 @@
       </c>
       <c r="K24" s="6">
         <f>COS(J10)</f>
-        <v>1</v>
+        <v>6.1257422745431001E-17</v>
       </c>
       <c r="L24" s="6">
         <f>-SIN(J10)*COS(K10)</f>
-        <v>0</v>
+        <v>-6.1257422745431001E-17</v>
       </c>
       <c r="M24" s="6">
         <f>SIN(J10)*SIN(K10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="6">
         <f>M10*COS(J10)</f>
@@ -3868,16 +3865,16 @@
       <c r="V24" s="24"/>
       <c r="W24" s="22">
         <f t="array" ref="W24:Z27">MMULT(W16:Z19,AG16:AJ19)</f>
-        <v>4.3315539021305322E-17</v>
+        <v>-1</v>
       </c>
       <c r="X24" s="6">
-        <v>0</v>
+        <v>1.2251484549086198E-16</v>
       </c>
       <c r="Y24" s="6">
-        <v>1</v>
+        <v>1.2251484549086203E-16</v>
       </c>
       <c r="Z24" s="6">
-        <v>663.5</v>
+        <v>598.5</v>
       </c>
       <c r="AA24" s="18"/>
       <c r="AB24" s="6">
@@ -3895,13 +3892,13 @@
       <c r="AF24" s="18"/>
       <c r="AG24" s="6">
         <f t="array" ref="AG24:AJ27">MMULT(W24:Z27,AB24:AE27)</f>
-        <v>4.3315539021305322E-17</v>
+        <v>-1</v>
       </c>
       <c r="AH24" s="6">
-        <v>0</v>
+        <v>1.2251484549086198E-16</v>
       </c>
       <c r="AI24" s="6">
-        <v>1</v>
+        <v>1.2251484549086203E-16</v>
       </c>
       <c r="AJ24" s="6">
         <v>598.5</v>
@@ -3942,15 +3939,15 @@
       </c>
       <c r="K25" s="6">
         <f>SIN(J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="6">
         <f>COS(J10)*COS(K10)</f>
-        <v>6.1257422745431001E-17</v>
+        <v>3.7524718414124473E-33</v>
       </c>
       <c r="M25" s="6">
         <f>-COS(J10)*SIN(K10)</f>
-        <v>-1</v>
+        <v>-6.1257422745431001E-17</v>
       </c>
       <c r="N25" s="6">
         <f>M10*SIN(J10)</f>
@@ -3958,16 +3955,16 @@
       </c>
       <c r="V25" s="24"/>
       <c r="W25" s="22">
-        <v>4.3315539021305316E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="X25" s="6">
         <v>1</v>
       </c>
       <c r="Y25" s="6">
-        <v>0</v>
+        <v>1.2251484549086198E-16</v>
       </c>
       <c r="Z25" s="6">
-        <v>-6.1257422745431001E-16</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="18"/>
       <c r="AB25" s="6">
@@ -3984,16 +3981,16 @@
       </c>
       <c r="AF25" s="18"/>
       <c r="AG25" s="6">
-        <v>4.3315539021305316E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="AH25" s="6">
         <v>1</v>
       </c>
       <c r="AI25" s="6">
-        <v>0</v>
+        <v>1.2251484549086198E-16</v>
       </c>
       <c r="AJ25" s="6">
-        <v>-6.1257422745431001E-16</v>
+        <v>-7.9634649569060285E-15</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.3">
@@ -4044,16 +4041,16 @@
       </c>
       <c r="V26" s="24"/>
       <c r="W26" s="22">
+        <v>-1.22514845490862E-16</v>
+      </c>
+      <c r="X26" s="6">
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="Y26" s="6">
         <v>-1</v>
       </c>
-      <c r="X26" s="6">
-        <v>4.3315539021305316E-17</v>
-      </c>
-      <c r="Y26" s="6">
-        <v>4.3315539021305322E-17</v>
-      </c>
       <c r="Z26" s="6">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="AA26" s="18"/>
       <c r="AB26" s="6">
@@ -4071,13 +4068,13 @@
       </c>
       <c r="AF26" s="18"/>
       <c r="AG26" s="6">
+        <v>-1.22514845490862E-16</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="AI26" s="6">
         <v>-1</v>
-      </c>
-      <c r="AH26" s="6">
-        <v>4.3315539021305316E-17</v>
-      </c>
-      <c r="AI26" s="6">
-        <v>4.3315539021305322E-17</v>
       </c>
       <c r="AJ26" s="6">
         <v>841</v>
@@ -4165,31 +4162,31 @@
       <c r="V29" s="24"/>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="G30" s="36" t="s">
+      <c r="C30" s="34"/>
+      <c r="G30" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="L30" s="36" t="s">
+      <c r="H30" s="34"/>
+      <c r="L30" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="M30" s="36"/>
+      <c r="M30" s="34"/>
       <c r="V30" s="24"/>
-      <c r="X30" s="36" t="s">
+      <c r="X30" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="Y30" s="36"/>
-      <c r="AC30" s="36" t="s">
+      <c r="Y30" s="34"/>
+      <c r="AC30" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="AD30" s="36"/>
-      <c r="AH30" s="36" t="s">
+      <c r="AD30" s="34"/>
+      <c r="AH30" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="AI30" s="36"/>
+      <c r="AI30" s="34"/>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
@@ -4211,14 +4208,14 @@
       <c r="M31" s="35"/>
       <c r="N31" s="35"/>
       <c r="V31" s="24"/>
-      <c r="X31" s="36" t="s">
+      <c r="X31" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="Y31" s="36"/>
-      <c r="AC31" s="36" t="s">
+      <c r="Y31" s="34"/>
+      <c r="AC31" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="AD31" s="36"/>
+      <c r="AD31" s="34"/>
       <c r="AG31" s="35" t="s">
         <v>33</v>
       </c>
@@ -4278,7 +4275,7 @@
       </c>
       <c r="Y32" s="6">
         <f>ATAN2(AJ24,AJ25)</f>
-        <v>-1.0235158353455473E-18</v>
+        <v>-1.3305705859492111E-17</v>
       </c>
       <c r="AC32" s="8" t="s">
         <v>78</v>
@@ -4293,11 +4290,11 @@
       </c>
       <c r="AH32" s="6">
         <f>-SIN(AC6)*COS(K6)</f>
-        <v>6.2697942212405134E-35</v>
+        <v>8.1507324876126662E-34</v>
       </c>
       <c r="AI32" s="6">
         <f>SIN(AC6)*SIN(K6)</f>
-        <v>1.0235158353455473E-18</v>
+        <v>1.3305705859492111E-17</v>
       </c>
       <c r="AJ32" s="6">
         <f>M6*COS(AC6)</f>
@@ -4359,7 +4356,7 @@
       </c>
       <c r="AG33" s="6">
         <f>SIN(AC6)</f>
-        <v>-1.0235158353455473E-18</v>
+        <v>-1.3305705859492111E-17</v>
       </c>
       <c r="AH33" s="6">
         <f>COS(AC6)*COS(K6)</f>
@@ -4371,7 +4368,7 @@
       </c>
       <c r="AJ33" s="6">
         <f>M6*SIN(AC6)</f>
-        <v>-2.4052622130620362E-17</v>
+        <v>-3.1268408769806462E-16</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.3">
@@ -4480,10 +4477,10 @@
         <v>1</v>
       </c>
       <c r="V35" s="24"/>
-      <c r="X35" s="36" t="s">
+      <c r="X35" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="Y35" s="36"/>
+      <c r="Y35" s="34"/>
       <c r="AC35" s="8" t="s">
         <v>89</v>
       </c>
@@ -4535,18 +4532,18 @@
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B38" s="36" t="s">
+      <c r="B38" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="36"/>
-      <c r="G38" s="36" t="s">
+      <c r="C38" s="34"/>
+      <c r="G38" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H38" s="36"/>
-      <c r="L38" s="36" t="s">
+      <c r="H38" s="34"/>
+      <c r="L38" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="M38" s="36"/>
+      <c r="M38" s="34"/>
       <c r="V38" s="24"/>
       <c r="X38" s="6">
         <f>(AJ24*COS(-Y32))-AJ25*SIN(-Y32)</f>
@@ -4665,18 +4662,18 @@
         <v>-4.594306705907325E-15</v>
       </c>
       <c r="V41" s="24"/>
-      <c r="X41" s="36" t="s">
+      <c r="X41" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="Y41" s="36"/>
-      <c r="AC41" s="36" t="s">
+      <c r="Y41" s="34"/>
+      <c r="AC41" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="AD41" s="36"/>
-      <c r="AH41" s="36" t="s">
+      <c r="AD41" s="34"/>
+      <c r="AH41" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="AI41" s="36"/>
+      <c r="AI41" s="34"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
@@ -4815,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="AI43" s="6">
-        <v>1.0235158353455473E-18</v>
+        <v>1.3305705859492111E-17</v>
       </c>
       <c r="AJ43" s="6">
         <v>23.500000000000039</v>
@@ -4861,13 +4858,13 @@
         <v>-6.1257422745431001E-17</v>
       </c>
       <c r="AH44" s="6">
-        <v>-1.0235158353455436E-18</v>
+        <v>-1.3305705859492108E-17</v>
       </c>
       <c r="AI44" s="6">
         <v>1</v>
       </c>
       <c r="AJ44" s="6">
-        <v>-3.9841377406660771E-14</v>
+        <v>-4.0130008872228212E-14</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.3">
@@ -4918,18 +4915,18 @@
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B46" s="36" t="s">
+      <c r="B46" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C46" s="36"/>
-      <c r="G46" s="36" t="s">
+      <c r="C46" s="34"/>
+      <c r="G46" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H46" s="36"/>
-      <c r="L46" s="36" t="s">
+      <c r="H46" s="34"/>
+      <c r="L46" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="M46" s="36"/>
+      <c r="M46" s="34"/>
       <c r="V46" s="24"/>
       <c r="W46" s="22">
         <v>0</v>
@@ -4994,136 +4991,136 @@
     <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <f t="array" ref="A48:D51">MMULT(K40:N43,K24:N27)</f>
-        <v>6.1257422745431001E-17</v>
+        <v>-1</v>
       </c>
       <c r="B48" s="6">
-        <v>-6.1257422745431001E-17</v>
+        <v>-7.5049436828248946E-33</v>
       </c>
       <c r="C48" s="6">
-        <v>1</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="D48" s="6">
         <v>598.5</v>
       </c>
       <c r="F48" s="6">
         <f t="array" ref="F48:I51">MMULT(A48:D51,A32:D35)</f>
-        <v>6.1257422745431001E-17</v>
+        <v>-1</v>
       </c>
       <c r="G48" s="6">
-        <v>-6.1257422745431001E-17</v>
+        <v>-7.5049436828248946E-33</v>
       </c>
       <c r="H48" s="6">
-        <v>1</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="I48" s="6">
-        <v>663.5</v>
+        <v>598.5</v>
       </c>
       <c r="K48" s="6">
         <f t="array" ref="K48:N51">MMULT(F48:I51,F32:I35)</f>
-        <v>6.1257422745431001E-17</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="6">
-        <v>-6.1257422745431001E-17</v>
+        <v>-7.5049436828248946E-33</v>
       </c>
       <c r="M48" s="6">
-        <v>1</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="N48" s="6">
-        <v>663.5</v>
+        <v>598.5</v>
       </c>
       <c r="V48" s="24"/>
     </row>
     <row r="49" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>6.1257422745431001E-17</v>
+        <v>3.7524718414124473E-33</v>
       </c>
       <c r="B49" s="6">
         <v>1</v>
       </c>
       <c r="C49" s="6">
-        <v>6.1257422745431001E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="D49" s="6">
         <v>-4.594306705907325E-15</v>
       </c>
       <c r="F49" s="6">
-        <v>6.1257422745431001E-17</v>
+        <v>3.7524718414124473E-33</v>
       </c>
       <c r="G49" s="6">
         <v>1</v>
       </c>
       <c r="H49" s="6">
-        <v>6.1257422745431001E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="I49" s="6">
-        <v>-6.1257422745431001E-16</v>
+        <v>3.369158250998705E-15</v>
       </c>
       <c r="K49" s="6">
-        <v>6.1257422745431001E-17</v>
+        <v>3.7524718414124473E-33</v>
       </c>
       <c r="L49" s="6">
         <v>1</v>
       </c>
       <c r="M49" s="6">
-        <v>6.1257422745431001E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="N49" s="6">
-        <v>-6.1257422745431001E-16</v>
+        <v>3.369158250998705E-15</v>
       </c>
       <c r="V49" s="24"/>
-      <c r="X49" s="36" t="s">
+      <c r="X49" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="Y49" s="36"/>
-      <c r="AB49" s="36" t="s">
+      <c r="Y49" s="34"/>
+      <c r="AB49" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="AC49" s="36"/>
-      <c r="AD49" s="36"/>
-      <c r="AE49" s="36"/>
-      <c r="AG49" s="36" t="s">
+      <c r="AC49" s="34"/>
+      <c r="AD49" s="34"/>
+      <c r="AE49" s="34"/>
+      <c r="AG49" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="AH49" s="36"/>
-      <c r="AI49" s="36"/>
-      <c r="AJ49" s="36"/>
+      <c r="AH49" s="34"/>
+      <c r="AI49" s="34"/>
+      <c r="AJ49" s="34"/>
     </row>
     <row r="50" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
+        <v>-1.22514845490862E-16</v>
+      </c>
+      <c r="B50" s="6">
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="C50" s="6">
         <v>-1</v>
-      </c>
-      <c r="B50" s="6">
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="C50" s="6">
-        <v>6.1257422745431001E-17</v>
       </c>
       <c r="D50" s="6">
         <v>841</v>
       </c>
       <c r="F50" s="6">
+        <v>-1.22514845490862E-16</v>
+      </c>
+      <c r="G50" s="6">
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="H50" s="6">
         <v>-1</v>
       </c>
-      <c r="G50" s="6">
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="H50" s="6">
-        <v>6.1257422745431001E-17</v>
-      </c>
       <c r="I50" s="6">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="K50" s="6">
+        <v>-1.22514845490862E-16</v>
+      </c>
+      <c r="L50" s="6">
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="M50" s="6">
         <v>-1</v>
       </c>
-      <c r="L50" s="6">
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="M50" s="6">
-        <v>6.1257422745431001E-17</v>
-      </c>
       <c r="N50" s="6">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="V50" s="24"/>
       <c r="W50" s="35" t="s">
@@ -5188,7 +5185,7 @@
         <v>6.1257422745431001E-17</v>
       </c>
       <c r="X51" s="6">
-        <v>-6.0233906910085458E-17</v>
+        <v>-4.7951716885938888E-17</v>
       </c>
       <c r="Y51" s="6">
         <v>1</v>
@@ -5215,13 +5212,13 @@
       <c r="AF51" s="18"/>
       <c r="AG51" s="6">
         <f t="array" ref="AG51:AI53">MMULT(AB51:AD53,W24:Y26)</f>
-        <v>1</v>
+        <v>6.1257422745431013E-17</v>
       </c>
       <c r="AH51" s="6">
-        <v>1.7941883724125684E-17</v>
+        <v>-6.1257422745430988E-17</v>
       </c>
       <c r="AI51" s="6">
-        <v>1.7941883724125678E-17</v>
+        <v>1</v>
       </c>
       <c r="AJ51" s="6" t="s">
         <v>52</v>
@@ -5236,15 +5233,15 @@
         <v>1</v>
       </c>
       <c r="Y52" s="6">
-        <v>6.0233906910085445E-17</v>
+        <v>4.7951716885938882E-17</v>
       </c>
       <c r="Z52" s="6">
-        <v>-3.9841377406660771E-14</v>
+        <v>-4.0130008872228212E-14</v>
       </c>
       <c r="AA52" s="18"/>
       <c r="AB52" s="6">
         <f>X51</f>
-        <v>-6.0233906910085458E-17</v>
+        <v>-4.7951716885938888E-17</v>
       </c>
       <c r="AC52" s="6">
         <f>X52</f>
@@ -5259,13 +5256,13 @@
       </c>
       <c r="AF52" s="18"/>
       <c r="AG52" s="6">
-        <v>-1.7941883724125684E-17</v>
+        <v>1.704665623768009E-16</v>
       </c>
       <c r="AH52" s="6">
         <v>1</v>
       </c>
       <c r="AI52" s="6">
-        <v>-6.0233906910085458E-17</v>
+        <v>6.1257422745430976E-17</v>
       </c>
       <c r="AJ52" s="6" t="s">
         <v>52</v>
@@ -5292,7 +5289,7 @@
       </c>
       <c r="AC53" s="6">
         <f>Y52</f>
-        <v>6.0233906910085445E-17</v>
+        <v>4.7951716885938882E-17</v>
       </c>
       <c r="AD53" s="6">
         <f>Y53</f>
@@ -5303,13 +5300,13 @@
       </c>
       <c r="AF53" s="18"/>
       <c r="AG53" s="6">
-        <v>-1.7941883724125678E-17</v>
+        <v>-1</v>
       </c>
       <c r="AH53" s="6">
-        <v>6.0233906910085445E-17</v>
+        <v>1.7046656237680085E-16</v>
       </c>
       <c r="AI53" s="6">
-        <v>1</v>
+        <v>6.1257422745431025E-17</v>
       </c>
       <c r="AJ53" s="6" t="s">
         <v>52</v>
@@ -5361,161 +5358,161 @@
       <c r="AE55" s="19"/>
     </row>
     <row r="56" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
-      <c r="B56" s="46"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
-      <c r="M56" s="46"/>
-      <c r="N56" s="46"/>
-      <c r="O56" s="46"/>
-      <c r="P56" s="46"/>
-      <c r="Q56" s="46"/>
-      <c r="R56" s="46"/>
-      <c r="S56" s="46"/>
-      <c r="T56" s="46"/>
-      <c r="U56" s="46"/>
-      <c r="V56" s="46"/>
-      <c r="W56" s="46"/>
-      <c r="X56" s="46"/>
-      <c r="Y56" s="46"/>
-      <c r="Z56" s="46"/>
-      <c r="AA56" s="46"/>
-      <c r="AB56" s="46"/>
-      <c r="AC56" s="46"/>
-      <c r="AD56" s="46"/>
-      <c r="AE56" s="46"/>
-      <c r="AF56" s="46"/>
-      <c r="AG56" s="46"/>
-      <c r="AH56" s="46"/>
-      <c r="AI56" s="46"/>
-      <c r="AJ56" s="46"/>
-      <c r="AK56" s="46"/>
-      <c r="AL56" s="46"/>
-      <c r="AM56" s="46"/>
-      <c r="AN56" s="46"/>
-      <c r="AO56" s="46"/>
-      <c r="AP56" s="46"/>
-      <c r="AQ56" s="46"/>
-      <c r="AR56" s="46"/>
-      <c r="AS56" s="46"/>
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="56"/>
+      <c r="K56" s="56"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="56"/>
+      <c r="N56" s="56"/>
+      <c r="O56" s="56"/>
+      <c r="P56" s="56"/>
+      <c r="Q56" s="56"/>
+      <c r="R56" s="56"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="56"/>
+      <c r="U56" s="56"/>
+      <c r="V56" s="56"/>
+      <c r="W56" s="56"/>
+      <c r="X56" s="56"/>
+      <c r="Y56" s="56"/>
+      <c r="Z56" s="56"/>
+      <c r="AA56" s="56"/>
+      <c r="AB56" s="56"/>
+      <c r="AC56" s="56"/>
+      <c r="AD56" s="56"/>
+      <c r="AE56" s="56"/>
+      <c r="AF56" s="56"/>
+      <c r="AG56" s="56"/>
+      <c r="AH56" s="56"/>
+      <c r="AI56" s="56"/>
+      <c r="AJ56" s="56"/>
+      <c r="AK56" s="56"/>
+      <c r="AL56" s="56"/>
+      <c r="AM56" s="56"/>
+      <c r="AN56" s="56"/>
+      <c r="AO56" s="56"/>
+      <c r="AP56" s="56"/>
+      <c r="AQ56" s="56"/>
+      <c r="AR56" s="56"/>
+      <c r="AS56" s="56"/>
     </row>
     <row r="57" spans="1:45" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="42" t="s">
+      <c r="A57" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="42"/>
-      <c r="K57" s="42"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="42"/>
-      <c r="N57" s="42"/>
-      <c r="O57" s="42"/>
-      <c r="P57" s="42"/>
-      <c r="Q57" s="42"/>
-      <c r="R57" s="42"/>
-      <c r="S57" s="42"/>
-      <c r="T57" s="42"/>
-      <c r="U57" s="42"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="49"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="49"/>
+      <c r="M57" s="49"/>
+      <c r="N57" s="49"/>
+      <c r="O57" s="49"/>
+      <c r="P57" s="49"/>
+      <c r="Q57" s="49"/>
+      <c r="R57" s="49"/>
+      <c r="S57" s="49"/>
+      <c r="T57" s="49"/>
+      <c r="U57" s="49"/>
       <c r="V57" s="24"/>
-      <c r="W57" s="42" t="s">
+      <c r="W57" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="X57" s="42"/>
-      <c r="Y57" s="42"/>
-      <c r="Z57" s="42"/>
-      <c r="AA57" s="42"/>
-      <c r="AB57" s="42"/>
-      <c r="AC57" s="42"/>
-      <c r="AD57" s="42"/>
-      <c r="AE57" s="42"/>
-      <c r="AF57" s="42"/>
-      <c r="AG57" s="42"/>
-      <c r="AH57" s="42"/>
-      <c r="AI57" s="42"/>
-      <c r="AJ57" s="42"/>
-      <c r="AK57" s="42"/>
-      <c r="AL57" s="42"/>
-      <c r="AM57" s="42"/>
-      <c r="AN57" s="42"/>
-      <c r="AO57" s="42"/>
-      <c r="AP57" s="42"/>
-      <c r="AQ57" s="42"/>
-      <c r="AR57" s="42"/>
-      <c r="AS57" s="42"/>
+      <c r="X57" s="49"/>
+      <c r="Y57" s="49"/>
+      <c r="Z57" s="49"/>
+      <c r="AA57" s="49"/>
+      <c r="AB57" s="49"/>
+      <c r="AC57" s="49"/>
+      <c r="AD57" s="49"/>
+      <c r="AE57" s="49"/>
+      <c r="AF57" s="49"/>
+      <c r="AG57" s="49"/>
+      <c r="AH57" s="49"/>
+      <c r="AI57" s="49"/>
+      <c r="AJ57" s="49"/>
+      <c r="AK57" s="49"/>
+      <c r="AL57" s="49"/>
+      <c r="AM57" s="49"/>
+      <c r="AN57" s="49"/>
+      <c r="AO57" s="49"/>
+      <c r="AP57" s="49"/>
+      <c r="AQ57" s="49"/>
+      <c r="AR57" s="49"/>
+      <c r="AS57" s="49"/>
     </row>
     <row r="58" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="43"/>
-      <c r="B58" s="43"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="43"/>
-      <c r="I58" s="43"/>
-      <c r="J58" s="43"/>
-      <c r="K58" s="43"/>
-      <c r="L58" s="43"/>
-      <c r="M58" s="43"/>
-      <c r="N58" s="43"/>
-      <c r="O58" s="43"/>
-      <c r="P58" s="43"/>
-      <c r="Q58" s="43"/>
-      <c r="R58" s="43"/>
-      <c r="S58" s="43"/>
-      <c r="T58" s="43"/>
-      <c r="U58" s="43"/>
+      <c r="A58" s="55"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="55"/>
+      <c r="D58" s="55"/>
+      <c r="E58" s="55"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
+      <c r="J58" s="55"/>
+      <c r="K58" s="55"/>
+      <c r="L58" s="55"/>
+      <c r="M58" s="55"/>
+      <c r="N58" s="55"/>
+      <c r="O58" s="55"/>
+      <c r="P58" s="55"/>
+      <c r="Q58" s="55"/>
+      <c r="R58" s="55"/>
+      <c r="S58" s="55"/>
+      <c r="T58" s="55"/>
+      <c r="U58" s="55"/>
       <c r="V58" s="24"/>
       <c r="AA58" s="16"/>
       <c r="AB58" s="16"/>
     </row>
     <row r="59" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A59" s="41" t="s">
+      <c r="A59" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="40"/>
-      <c r="F59" s="40" t="s">
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="F59" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
-      <c r="K59" s="34" t="s">
+      <c r="G59" s="58"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="58"/>
+      <c r="K59" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="L59" s="34"/>
-      <c r="M59" s="34"/>
-      <c r="N59" s="34"/>
-      <c r="O59" s="34"/>
-      <c r="P59" s="34"/>
+      <c r="L59" s="57"/>
+      <c r="M59" s="57"/>
+      <c r="N59" s="57"/>
+      <c r="O59" s="57"/>
+      <c r="P59" s="57"/>
       <c r="V59" s="24"/>
     </row>
     <row r="60" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="37" t="s">
+      <c r="A60" s="52" t="s">
         <v>110</v>
       </c>
       <c r="B60" s="6">
-        <f t="shared" ref="B60:B62" si="4">M32</f>
-        <v>0</v>
-      </c>
-      <c r="C60" s="37" t="s">
+        <f t="shared" ref="B60:B62" si="3">M32</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="52" t="s">
         <v>113</v>
       </c>
       <c r="D60" s="6">
@@ -5536,23 +5533,23 @@
       </c>
       <c r="K60" s="6">
         <f>H61</f>
-        <v>650</v>
+        <v>585</v>
       </c>
       <c r="L60" s="6">
         <f>H64</f>
-        <v>-2.4015819785039663E-30</v>
+        <v>-65</v>
       </c>
       <c r="M60" s="6">
         <f>H67</f>
-        <v>-2.4015819785039663E-30</v>
+        <v>-3.9817324784530174E-15</v>
       </c>
       <c r="N60" s="26">
         <f>H70</f>
-        <v>-2.4391066969180907E-31</v>
+        <v>-65</v>
       </c>
       <c r="O60" s="6">
         <f>H73</f>
-        <v>-2.4391066969180907E-31</v>
+        <v>0</v>
       </c>
       <c r="P60" s="6">
         <f>H76</f>
@@ -5561,49 +5558,49 @@
       <c r="V60" s="24"/>
     </row>
     <row r="61" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A61" s="38"/>
+      <c r="A61" s="53"/>
       <c r="B61" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="C61" s="38"/>
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="C61" s="53"/>
       <c r="D61" s="6">
         <f>M41</f>
         <v>1</v>
       </c>
-      <c r="F61" s="37" t="s">
+      <c r="F61" s="52" t="s">
         <v>3</v>
       </c>
       <c r="G61" s="6">
         <f>N48-B72</f>
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="H61" s="26">
         <f>B61*G63-B62*G62</f>
-        <v>650</v>
+        <v>585</v>
       </c>
       <c r="I61" s="26">
-        <f t="shared" ref="I61:I69" si="5">B60</f>
+        <f t="shared" ref="I61:I69" si="4">B60</f>
         <v>0</v>
       </c>
       <c r="K61" s="6">
         <f>H62</f>
-        <v>3.920475055707584E-14</v>
+        <v>3.5223018078622825E-14</v>
       </c>
       <c r="L61" s="6">
         <v>0</v>
       </c>
       <c r="M61" s="6">
         <f>H68</f>
-        <v>3.920475055707584E-14</v>
+        <v>65.000000000000028</v>
       </c>
       <c r="N61" s="26">
         <f>H71</f>
-        <v>3.981732478453015E-15</v>
+        <v>0</v>
       </c>
       <c r="O61" s="6">
         <f>H74</f>
-        <v>3.981732478453015E-15</v>
+        <v>7.9634649569060301E-15</v>
       </c>
       <c r="P61" s="6">
         <f>H77</f>
@@ -5612,48 +5609,48 @@
       <c r="V61" s="24"/>
     </row>
     <row r="62" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A62" s="39"/>
+      <c r="A62" s="54"/>
       <c r="B62" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.1257422745431001E-17</v>
       </c>
-      <c r="C62" s="39"/>
+      <c r="C62" s="54"/>
       <c r="D62" s="6">
         <f>M42</f>
         <v>6.1257422745431001E-17</v>
       </c>
-      <c r="F62" s="38"/>
+      <c r="F62" s="53"/>
       <c r="G62" s="6">
         <f>N49-B73</f>
-        <v>-6.1257422745431001E-16</v>
+        <v>3.369158250998705E-15</v>
       </c>
       <c r="H62" s="6">
         <f>B62*G61-B60*G63</f>
-        <v>3.920475055707584E-14</v>
+        <v>3.5223018078622825E-14</v>
       </c>
       <c r="I62" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K62" s="6">
         <f>H63</f>
-        <v>-640</v>
+        <v>-575</v>
       </c>
       <c r="L62" s="6">
         <f>H66</f>
-        <v>-640</v>
+        <v>-575</v>
       </c>
       <c r="M62" s="6">
         <f>H69</f>
-        <v>0</v>
+        <v>7.9634649569060301E-15</v>
       </c>
       <c r="N62" s="26">
         <f>H72</f>
-        <v>-65</v>
+        <v>0</v>
       </c>
       <c r="O62" s="6">
         <f>H75</f>
-        <v>0</v>
+        <v>9.756426787672363E-31</v>
       </c>
       <c r="P62" s="6">
         <f>H78</f>
@@ -5662,31 +5659,31 @@
       <c r="V62" s="24"/>
     </row>
     <row r="63" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A63" s="37" t="s">
+      <c r="A63" s="52" t="s">
         <v>111</v>
       </c>
       <c r="B63" s="6">
         <f>C40</f>
         <v>0</v>
       </c>
-      <c r="C63" s="37" t="s">
+      <c r="C63" s="52" t="s">
         <v>114</v>
       </c>
       <c r="D63" s="6">
         <f>C48</f>
-        <v>1</v>
-      </c>
-      <c r="F63" s="39"/>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="F63" s="54"/>
       <c r="G63" s="6">
         <f>N50-B74</f>
-        <v>650</v>
+        <v>585</v>
       </c>
       <c r="H63" s="6">
         <f>B60*G62-B61*G61</f>
-        <v>-640</v>
+        <v>-575</v>
       </c>
       <c r="I63" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.1257422745431001E-17</v>
       </c>
       <c r="K63" s="6">
@@ -5707,38 +5704,38 @@
       </c>
       <c r="O63" s="6">
         <f>I73</f>
-        <v>1</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="P63" s="6">
         <f>I76</f>
-        <v>1</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="V63" s="24"/>
     </row>
     <row r="64" spans="1:45" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="38"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="6">
         <f>C41</f>
         <v>1</v>
       </c>
-      <c r="C64" s="38"/>
+      <c r="C64" s="53"/>
       <c r="D64" s="6">
         <f>C49</f>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="F64" s="37" t="s">
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="F64" s="52" t="s">
         <v>4</v>
       </c>
       <c r="G64" s="6">
         <f>N48-B75</f>
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="H64" s="26">
         <f>B64*G66-B65*G65</f>
-        <v>-2.4015819785039663E-30</v>
+        <v>-65</v>
       </c>
       <c r="I64" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K64" s="6">
@@ -5759,36 +5756,36 @@
       </c>
       <c r="O64" s="6">
         <f>I74</f>
-        <v>6.1257422745431001E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="P64" s="6">
         <f>I77</f>
-        <v>6.1257422745431001E-17</v>
+        <v>1.22514845490862E-16</v>
       </c>
       <c r="V64" s="24"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A65" s="39"/>
+      <c r="A65" s="54"/>
       <c r="B65" s="6">
         <f>C42</f>
         <v>6.1257422745431001E-17</v>
       </c>
-      <c r="C65" s="39"/>
+      <c r="C65" s="54"/>
       <c r="D65" s="6">
         <f>C50</f>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="F65" s="38"/>
+        <v>-1</v>
+      </c>
+      <c r="F65" s="53"/>
       <c r="G65" s="6">
         <f>N49-B76</f>
-        <v>3.920475055707584E-14</v>
+        <v>4.3186483035528855E-14</v>
       </c>
       <c r="H65" s="6">
         <f>B65*G64-B63*G66</f>
-        <v>3.920475055707584E-14</v>
+        <v>3.5223018078622825E-14</v>
       </c>
       <c r="I65" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K65" s="6">
@@ -5809,389 +5806,389 @@
       </c>
       <c r="O65" s="6">
         <f>I75</f>
-        <v>6.1257422745431001E-17</v>
+        <v>-1</v>
       </c>
       <c r="P65" s="6">
         <f>I78</f>
-        <v>6.1257422745431001E-17</v>
+        <v>-1</v>
       </c>
       <c r="V65" s="24"/>
     </row>
     <row r="66" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="37" t="s">
+      <c r="A66" s="52" t="s">
         <v>112</v>
       </c>
       <c r="B66" s="6">
         <f>H40</f>
         <v>1</v>
       </c>
-      <c r="C66" s="37" t="s">
+      <c r="C66" s="52" t="s">
         <v>119</v>
       </c>
       <c r="D66" s="6">
         <f>H48</f>
-        <v>1</v>
-      </c>
-      <c r="F66" s="39"/>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="F66" s="54"/>
       <c r="G66" s="6">
         <f>N50-B77</f>
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="H66" s="6">
         <f>B63*G65-B64*G64</f>
-        <v>-640</v>
+        <v>-575</v>
       </c>
       <c r="I66" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.1257422745431001E-17</v>
       </c>
       <c r="V66" s="24"/>
     </row>
     <row r="67" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="38"/>
+      <c r="A67" s="53"/>
       <c r="B67" s="6">
         <f>H41</f>
         <v>6.1257422745431001E-17</v>
       </c>
-      <c r="C67" s="38"/>
+      <c r="C67" s="53"/>
       <c r="D67" s="6">
         <f>H49</f>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="F67" s="37" t="s">
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="F67" s="52" t="s">
         <v>5</v>
       </c>
       <c r="G67" s="6">
         <f>N48-B78</f>
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="H67" s="26">
         <f>B67*G69-B68*G68</f>
-        <v>-2.4015819785039663E-30</v>
+        <v>-3.9817324784530174E-15</v>
       </c>
       <c r="I67" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="V67" s="24"/>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A68" s="39"/>
+      <c r="A68" s="54"/>
       <c r="B68" s="6">
         <f>H42</f>
         <v>6.1257422745431001E-17</v>
       </c>
-      <c r="C68" s="39"/>
+      <c r="C68" s="54"/>
       <c r="D68" s="6">
         <f>H50</f>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="F68" s="38"/>
+        <v>-1</v>
+      </c>
+      <c r="F68" s="53"/>
       <c r="G68" s="6">
         <f>N49-B79</f>
-        <v>3.920475055707584E-14</v>
+        <v>4.3186483035528855E-14</v>
       </c>
       <c r="H68" s="6">
         <f>B68*G67-B66*G69</f>
-        <v>3.920475055707584E-14</v>
+        <v>65.000000000000028</v>
       </c>
       <c r="I68" s="6">
+        <f t="shared" si="4"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M68" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="N68" s="57"/>
+      <c r="V68" s="24"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F69" s="54"/>
+      <c r="G69" s="6">
+        <f>N50-B80</f>
+        <v>-65</v>
+      </c>
+      <c r="H69" s="6">
+        <f>B66*G68-B67*G67</f>
+        <v>7.9634649569060301E-15</v>
+      </c>
+      <c r="I69" s="6">
+        <f t="shared" si="4"/>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="M69" s="28" t="str">
+        <f>IF(N69=0, "S", "N")</f>
+        <v>N</v>
+      </c>
+      <c r="N69" s="17">
+        <f>MDETERM(K60:P65)</f>
+        <v>-2.9763450276436287E-9</v>
+      </c>
+      <c r="V69" s="24"/>
+    </row>
+    <row r="70" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F70" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="6">
+        <f>N48-D72</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="26">
+        <f>D61*G72-D62*G71</f>
+        <v>-65</v>
+      </c>
+      <c r="I70" s="6">
+        <f t="shared" ref="I70:I78" si="5">D60</f>
+        <v>0</v>
+      </c>
+      <c r="V70" s="24"/>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A71" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="6">
+        <f>N49-D73</f>
+        <v>7.9634649569060301E-15</v>
+      </c>
+      <c r="H71" s="6">
+        <f>D62*G70-D60*G72</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="V71" s="24"/>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A72" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="6">
+        <f t="shared" ref="B72:B74" si="6">N32</f>
+        <v>23.5</v>
+      </c>
+      <c r="C72" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="6">
+        <f t="shared" ref="D72:D74" si="7">N40</f>
+        <v>598.5</v>
+      </c>
+      <c r="F72" s="54"/>
+      <c r="G72" s="6">
+        <f>N50-D74</f>
+        <v>-65</v>
+      </c>
+      <c r="H72" s="6">
+        <f>D60*G71-D61*G70</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="6">
         <f t="shared" si="5"/>
         <v>6.1257422745431001E-17</v>
       </c>
-      <c r="M68" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="N68" s="34"/>
-      <c r="V68" s="24"/>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="F69" s="39"/>
-      <c r="G69" s="6">
-        <f>N50-B80</f>
-        <v>0</v>
-      </c>
-      <c r="H69" s="6">
-        <f>B66*G68-B67*G67</f>
-        <v>0</v>
-      </c>
-      <c r="I69" s="6">
-        <f t="shared" si="5"/>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="M69" s="28" t="str">
-        <f>IF(N69=0, "S", "N")</f>
-        <v>S</v>
-      </c>
-      <c r="N69" s="17">
-        <f>MDETERM(K60:P65)</f>
-        <v>0</v>
-      </c>
-      <c r="V69" s="24"/>
-    </row>
-    <row r="70" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F70" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="6">
-        <f>N48-D72</f>
-        <v>65</v>
-      </c>
-      <c r="H70" s="26">
-        <f>D61*G72-D62*G71</f>
-        <v>-2.4391066969180907E-31</v>
-      </c>
-      <c r="I70" s="6">
-        <f t="shared" ref="I70:I78" si="6">D60</f>
-        <v>0</v>
-      </c>
-      <c r="V70" s="24"/>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A71" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="6">
-        <f>N49-D73</f>
-        <v>3.981732478453015E-15</v>
-      </c>
-      <c r="H71" s="6">
-        <f>D62*G70-D60*G72</f>
-        <v>3.981732478453015E-15</v>
-      </c>
-      <c r="I71" s="6">
+      <c r="V72" s="24"/>
+    </row>
+    <row r="73" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="53"/>
+      <c r="B73" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="V71" s="24"/>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A72" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="B72" s="6">
-        <f t="shared" ref="B72:B74" si="7">N32</f>
-        <v>23.5</v>
-      </c>
-      <c r="C72" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="D72" s="6">
-        <f t="shared" ref="D72:D74" si="8">N40</f>
-        <v>598.5</v>
-      </c>
-      <c r="F72" s="39"/>
-      <c r="G72" s="6">
-        <f>N50-D74</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="6">
-        <f>D60*G71-D61*G70</f>
-        <v>-65</v>
-      </c>
-      <c r="I72" s="6">
-        <f t="shared" si="6"/>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="V72" s="24"/>
-    </row>
-    <row r="73" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="38"/>
-      <c r="B73" s="6">
+        <v>0</v>
+      </c>
+      <c r="C73" s="53"/>
+      <c r="D73" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="C73" s="38"/>
-      <c r="D73" s="6">
-        <f t="shared" si="8"/>
         <v>-4.594306705907325E-15</v>
       </c>
-      <c r="F73" s="37" t="s">
+      <c r="F73" s="52" t="s">
         <v>7</v>
       </c>
       <c r="G73" s="6">
         <f>N48-D75</f>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H73" s="26">
         <f>D64*G75-D65*G74</f>
-        <v>-2.4391066969180907E-31</v>
+        <v>0</v>
       </c>
       <c r="I73" s="6">
+        <f t="shared" si="5"/>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="V73" s="24"/>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A74" s="54"/>
+      <c r="B74" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="V73" s="24"/>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A74" s="39"/>
-      <c r="B74" s="6">
+        <v>191</v>
+      </c>
+      <c r="C74" s="54"/>
+      <c r="D74" s="6">
         <f t="shared" si="7"/>
-        <v>191</v>
-      </c>
-      <c r="C74" s="39"/>
-      <c r="D74" s="6">
+        <v>841</v>
+      </c>
+      <c r="F74" s="53"/>
+      <c r="G74" s="6">
+        <f>N49-D76</f>
+        <v>7.9634649569060301E-15</v>
+      </c>
+      <c r="H74" s="6">
+        <f>D65*G73-D63*G75</f>
+        <v>7.9634649569060301E-15</v>
+      </c>
+      <c r="I74" s="6">
+        <f t="shared" si="5"/>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="O74"/>
+      <c r="V74" s="24"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A75" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" s="6">
+        <f t="shared" ref="B75:B77" si="8">D40</f>
+        <v>23.500000000000039</v>
+      </c>
+      <c r="C75" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" s="6">
+        <f t="shared" ref="D75:D77" si="9">D48</f>
+        <v>598.5</v>
+      </c>
+      <c r="F75" s="54"/>
+      <c r="G75" s="6">
+        <f>N50-D77</f>
+        <v>-65</v>
+      </c>
+      <c r="H75" s="6">
+        <f>D63*G74-D64*G73</f>
+        <v>9.756426787672363E-31</v>
+      </c>
+      <c r="I75" s="6">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="V75" s="24"/>
+    </row>
+    <row r="76" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="53"/>
+      <c r="B76" s="6">
+        <f t="shared" si="8"/>
+        <v>-3.981732478453015E-14</v>
+      </c>
+      <c r="C76" s="53"/>
+      <c r="D76" s="6">
+        <f t="shared" si="9"/>
+        <v>-4.594306705907325E-15</v>
+      </c>
+      <c r="F76" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="6">
+        <f>N48-D78</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="26">
+        <f>D67*G78-D68*G77</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="6">
+        <f t="shared" si="5"/>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="R76"/>
+      <c r="V76" s="24"/>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A77" s="54"/>
+      <c r="B77" s="6">
         <f t="shared" si="8"/>
         <v>841</v>
       </c>
-      <c r="F74" s="38"/>
-      <c r="G74" s="6">
-        <f>N49-D76</f>
-        <v>3.981732478453015E-15</v>
-      </c>
-      <c r="H74" s="6">
-        <f>D65*G73-D63*G75</f>
-        <v>3.981732478453015E-15</v>
-      </c>
-      <c r="I74" s="6">
-        <f t="shared" si="6"/>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="O74"/>
-      <c r="V74" s="24"/>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A75" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="B75" s="6">
-        <f t="shared" ref="B75:B77" si="9">D40</f>
-        <v>23.500000000000039</v>
-      </c>
-      <c r="C75" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" s="6">
-        <f t="shared" ref="D75:D77" si="10">D48</f>
-        <v>598.5</v>
-      </c>
-      <c r="F75" s="39"/>
-      <c r="G75" s="6">
-        <f>N50-D77</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="6">
-        <f>D63*G74-D64*G73</f>
-        <v>0</v>
-      </c>
-      <c r="I75" s="6">
-        <f t="shared" si="6"/>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="V75" s="24"/>
-    </row>
-    <row r="76" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="38"/>
-      <c r="B76" s="6">
-        <f t="shared" si="9"/>
-        <v>-3.981732478453015E-14</v>
-      </c>
-      <c r="C76" s="38"/>
-      <c r="D76" s="6">
-        <f t="shared" si="10"/>
-        <v>-4.594306705907325E-15</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="G76" s="6">
-        <f>N48-D78</f>
-        <v>0</v>
-      </c>
-      <c r="H76" s="26">
-        <f>D67*G78-D68*G77</f>
-        <v>0</v>
-      </c>
-      <c r="I76" s="6">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="R76"/>
-      <c r="V76" s="24"/>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A77" s="39"/>
-      <c r="B77" s="6">
+      <c r="C77" s="54"/>
+      <c r="D77" s="6">
         <f t="shared" si="9"/>
         <v>841</v>
       </c>
-      <c r="C77" s="39"/>
-      <c r="D77" s="6">
+      <c r="F77" s="53"/>
+      <c r="G77" s="6">
+        <f>N49-D79</f>
+        <v>0</v>
+      </c>
+      <c r="H77" s="6">
+        <f>D68*G76-D66*G78</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="6">
+        <f t="shared" si="5"/>
+        <v>1.22514845490862E-16</v>
+      </c>
+      <c r="V77" s="24"/>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A78" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="6">
+        <f t="shared" ref="B78:B80" si="10">I40</f>
+        <v>23.500000000000039</v>
+      </c>
+      <c r="C78" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="D78" s="6">
+        <f t="shared" ref="D78:D80" si="11">I48</f>
+        <v>598.5</v>
+      </c>
+      <c r="F78" s="54"/>
+      <c r="G78" s="6">
+        <f>N50-D80</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="6">
+        <f>D66*G77-D67*G76</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="6">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="V78" s="24"/>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A79" s="53"/>
+      <c r="B79" s="6">
+        <f t="shared" si="10"/>
+        <v>-3.981732478453015E-14</v>
+      </c>
+      <c r="C79" s="53"/>
+      <c r="D79" s="6">
+        <f t="shared" si="11"/>
+        <v>3.369158250998705E-15</v>
+      </c>
+      <c r="V79" s="24"/>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A80" s="54"/>
+      <c r="B80" s="6">
         <f t="shared" si="10"/>
         <v>841</v>
       </c>
-      <c r="F77" s="38"/>
-      <c r="G77" s="6">
-        <f>N49-D79</f>
-        <v>0</v>
-      </c>
-      <c r="H77" s="6">
-        <f>D68*G76-D66*G78</f>
-        <v>0</v>
-      </c>
-      <c r="I77" s="6">
-        <f t="shared" si="6"/>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="V77" s="24"/>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A78" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="B78" s="6">
-        <f t="shared" ref="B78:B80" si="11">I40</f>
-        <v>23.500000000000039</v>
-      </c>
-      <c r="C78" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="D78" s="6">
-        <f t="shared" ref="D78:D80" si="12">I48</f>
-        <v>663.5</v>
-      </c>
-      <c r="F78" s="39"/>
-      <c r="G78" s="6">
-        <f>N50-D80</f>
-        <v>0</v>
-      </c>
-      <c r="H78" s="6">
-        <f>D66*G77-D67*G76</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="6">
-        <f t="shared" si="6"/>
-        <v>6.1257422745431001E-17</v>
-      </c>
-      <c r="V78" s="24"/>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A79" s="38"/>
-      <c r="B79" s="6">
+      <c r="C80" s="54"/>
+      <c r="D80" s="6">
         <f t="shared" si="11"/>
-        <v>-3.981732478453015E-14</v>
-      </c>
-      <c r="C79" s="38"/>
-      <c r="D79" s="6">
-        <f t="shared" si="12"/>
-        <v>-6.1257422745431001E-16</v>
-      </c>
-      <c r="V79" s="24"/>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A80" s="39"/>
-      <c r="B80" s="6">
-        <f t="shared" si="11"/>
-        <v>841</v>
-      </c>
-      <c r="C80" s="39"/>
-      <c r="D80" s="6">
-        <f t="shared" si="12"/>
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="V80" s="24"/>
     </row>
@@ -6206,51 +6203,54 @@
     </row>
   </sheetData>
   <mergeCells count="117">
-    <mergeCell ref="AH14:AI14"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="AB15:AE15"/>
-    <mergeCell ref="AG15:AJ15"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="AC30:AD30"/>
-    <mergeCell ref="AG23:AJ23"/>
-    <mergeCell ref="W15:Z15"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="AB23:AE23"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="AC14:AD14"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="W3:Y3"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="F70:F72"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="F67:F69"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="K59:P59"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A57:U57"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="W2:AS2"/>
+    <mergeCell ref="A58:U58"/>
+    <mergeCell ref="AG49:AJ49"/>
+    <mergeCell ref="AG50:AJ50"/>
+    <mergeCell ref="AB49:AE49"/>
+    <mergeCell ref="AB50:AE50"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="W57:AS57"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A56:AS56"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="K47:N47"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="K23:N23"/>
     <mergeCell ref="W1:AS1"/>
     <mergeCell ref="AG42:AJ42"/>
     <mergeCell ref="W50:Z50"/>
@@ -6275,54 +6275,51 @@
     <mergeCell ref="I3:M3"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="G6:G8"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A57:U57"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="W2:AS2"/>
-    <mergeCell ref="A58:U58"/>
-    <mergeCell ref="AG49:AJ49"/>
-    <mergeCell ref="AG50:AJ50"/>
-    <mergeCell ref="AB49:AE49"/>
-    <mergeCell ref="AB50:AE50"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="W57:AS57"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A56:AS56"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="K47:N47"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="M68:N68"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="F70:F72"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="F76:F78"/>
-    <mergeCell ref="F61:F63"/>
-    <mergeCell ref="F64:F66"/>
-    <mergeCell ref="F67:F69"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="K59:P59"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="AB23:AE23"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AH14:AI14"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="AB15:AE15"/>
+    <mergeCell ref="AG15:AJ15"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="AC30:AD30"/>
+    <mergeCell ref="AG23:AJ23"/>
+    <mergeCell ref="W15:Z15"/>
+    <mergeCell ref="X14:Y14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
